--- a/calendar_chilean_2025A.xlsx
+++ b/calendar_chilean_2025A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed268546/Dropbox/Mac/Documents/codes/SPOCK_chilean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A367E13-0787-014E-B123-84F519D07B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC776B90-9518-1E40-BD46-20E2291F2D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5920" yWindow="500" windowWidth="29060" windowHeight="20840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -64,12 +64,6 @@
     <t>Observed</t>
   </si>
   <si>
-    <t>nights Pignata</t>
-  </si>
-  <si>
-    <t>nights Caceres</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total </t>
   </si>
   <si>
@@ -77,6 +71,33 @@
   </si>
   <si>
     <t>nights Schreiber </t>
+  </si>
+  <si>
+    <t>Rabus</t>
+  </si>
+  <si>
+    <t>Schreiber </t>
+  </si>
+  <si>
+    <t>Chacón</t>
+  </si>
+  <si>
+    <t>nights Toloza</t>
+  </si>
+  <si>
+    <t>nights Chacón</t>
+  </si>
+  <si>
+    <t>nights Rabus</t>
+  </si>
+  <si>
+    <t>Toloza</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>False</t>
   </si>
 </sst>
 </file>
@@ -124,7 +145,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,8 +164,38 @@
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5D6FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor theme="9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="39">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -318,39 +369,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -421,117 +439,14 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -540,26 +455,11 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,10 +469,10 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -580,26 +480,13 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -608,14 +495,14 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,14 +510,12 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,24 +523,112 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
         <color indexed="64"/>
@@ -666,7 +639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -692,12 +665,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -707,15 +674,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -730,65 +688,77 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -818,6 +788,12 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFCBDD1"/>
+      <color rgb="FFF5D6FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1064,7 +1040,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>7</v>
@@ -1074,10 +1050,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24">
+      <c r="A2" s="19">
         <v>45748</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="15">
         <v>1</v>
       </c>
       <c r="C2" s="5">
@@ -1089,17 +1065,25 @@
       <c r="E2" s="6">
         <v>0</v>
       </c>
-      <c r="F2" s="44"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="30"/>
+      <c r="F2" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="41"/>
+      <c r="J2" s="42" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="25">
+      <c r="A3" s="20">
         <v>45749</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="16">
         <v>1</v>
       </c>
       <c r="C3" s="7">
@@ -1111,17 +1095,25 @@
       <c r="E3" s="8">
         <v>0</v>
       </c>
-      <c r="F3" s="45"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="31"/>
+      <c r="F3" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="14"/>
+      <c r="J3" s="43" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25">
+      <c r="A4" s="20">
         <v>45750</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="16">
         <v>1</v>
       </c>
       <c r="C4" s="7">
@@ -1133,17 +1125,23 @@
       <c r="E4" s="8">
         <v>0</v>
       </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="31"/>
+      <c r="F4" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="14"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="25">
+      <c r="A5" s="20">
         <v>45751</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="17">
         <v>0</v>
       </c>
       <c r="C5" s="7">
@@ -1155,17 +1153,17 @@
       <c r="E5" s="8">
         <v>0</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="32"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25">
+      <c r="A6" s="20">
         <v>45752</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="17">
         <v>0</v>
       </c>
       <c r="C6" s="7">
@@ -1177,17 +1175,17 @@
       <c r="E6" s="8">
         <v>0</v>
       </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="32"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="44"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="25">
+      <c r="A7" s="20">
         <v>45753</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="17">
         <v>0</v>
       </c>
       <c r="C7" s="7">
@@ -1199,17 +1197,17 @@
       <c r="E7" s="8">
         <v>0</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="32"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="44"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="25">
+      <c r="A8" s="20">
         <v>45754</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="17">
         <v>0</v>
       </c>
       <c r="C8" s="7">
@@ -1221,17 +1219,17 @@
       <c r="E8" s="8">
         <v>0</v>
       </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="32"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="44"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="25">
+      <c r="A9" s="20">
         <v>45755</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="17">
         <v>0</v>
       </c>
       <c r="C9" s="7">
@@ -1243,20 +1241,20 @@
       <c r="E9" s="8">
         <v>0</v>
       </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="32"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="44"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="25">
+      <c r="A10" s="20">
         <v>45756</v>
       </c>
-      <c r="B10" s="22">
-        <v>0</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="B10" s="17">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
         <v>1</v>
       </c>
       <c r="D10" s="7">
@@ -1265,20 +1263,26 @@
       <c r="E10" s="8">
         <v>0</v>
       </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="31"/>
+      <c r="F10" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="43"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="25">
+      <c r="A11" s="20">
         <v>45757</v>
       </c>
-      <c r="B11" s="22">
-        <v>0</v>
-      </c>
-      <c r="C11" s="11">
+      <c r="B11" s="17">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
         <v>1</v>
       </c>
       <c r="D11" s="7">
@@ -1287,20 +1291,26 @@
       <c r="E11" s="8">
         <v>0</v>
       </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="31"/>
+      <c r="F11" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="43"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="25">
+      <c r="A12" s="20">
         <v>45758</v>
       </c>
-      <c r="B12" s="22">
-        <v>0</v>
-      </c>
-      <c r="C12" s="11">
+      <c r="B12" s="17">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
         <v>1</v>
       </c>
       <c r="D12" s="7">
@@ -1309,17 +1319,25 @@
       <c r="E12" s="8">
         <v>0</v>
       </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="31"/>
+      <c r="F12" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="43" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25">
+      <c r="A13" s="20">
         <v>45759</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="17">
         <v>0</v>
       </c>
       <c r="C13" s="7">
@@ -1331,17 +1349,17 @@
       <c r="E13" s="8">
         <v>0</v>
       </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="31"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="25">
+      <c r="A14" s="20">
         <v>45760</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="17">
         <v>0</v>
       </c>
       <c r="C14" s="7">
@@ -1353,17 +1371,17 @@
       <c r="E14" s="8">
         <v>0</v>
       </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="31"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="43"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="25">
+      <c r="A15" s="20">
         <v>45761</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="17">
         <v>0</v>
       </c>
       <c r="C15" s="7">
@@ -1375,17 +1393,17 @@
       <c r="E15" s="8">
         <v>0</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="32"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="44"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="25">
+      <c r="A16" s="20">
         <v>45762</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="17">
         <v>0</v>
       </c>
       <c r="C16" s="7">
@@ -1397,21 +1415,21 @@
       <c r="E16" s="8">
         <v>0</v>
       </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="32"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="44"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25">
+      <c r="A17" s="20">
         <v>45763</v>
       </c>
-      <c r="B17" s="22">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0</v>
+      <c r="B17" s="17">
+        <v>0</v>
+      </c>
+      <c r="C17" s="48">
+        <v>1</v>
       </c>
       <c r="D17" s="7">
         <v>0</v>
@@ -1419,83 +1437,105 @@
       <c r="E17" s="8">
         <v>0</v>
       </c>
-      <c r="F17" s="47"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="32"/>
+      <c r="F17" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="14"/>
+      <c r="J17" s="44"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="25">
+      <c r="A18" s="20">
         <v>45764</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="17">
         <v>0</v>
       </c>
       <c r="C18" s="7">
         <v>0</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="9">
         <v>1</v>
       </c>
       <c r="E18" s="8">
         <v>0</v>
       </c>
-      <c r="F18" s="48"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="31"/>
+      <c r="F18" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="14"/>
+      <c r="J18" s="43"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="25">
+      <c r="A19" s="20">
         <v>45765</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="17">
         <v>0</v>
       </c>
       <c r="C19" s="7">
         <v>0</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="9">
         <v>1</v>
       </c>
       <c r="E19" s="8">
         <v>0</v>
       </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="31"/>
+      <c r="F19" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="14"/>
+      <c r="J19" s="43"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="25">
+      <c r="A20" s="20">
         <v>45766</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="17">
         <v>0</v>
       </c>
       <c r="C20" s="7">
         <v>0</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="9">
         <v>1</v>
       </c>
       <c r="E20" s="8">
         <v>0</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="31"/>
+      <c r="F20" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="43"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="25">
+      <c r="A21" s="20">
         <v>45767</v>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="17">
         <v>0</v>
       </c>
       <c r="C21" s="7">
@@ -1507,17 +1547,17 @@
       <c r="E21" s="8">
         <v>0</v>
       </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="31"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="43"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="25">
+      <c r="A22" s="20">
         <v>45768</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="17">
         <v>0</v>
       </c>
       <c r="C22" s="7">
@@ -1529,17 +1569,17 @@
       <c r="E22" s="8">
         <v>0</v>
       </c>
-      <c r="F22" s="46"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="31"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="43"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25">
+      <c r="A23" s="20">
         <v>45769</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="17">
         <v>0</v>
       </c>
       <c r="C23" s="7">
@@ -1551,17 +1591,17 @@
       <c r="E23" s="8">
         <v>0</v>
       </c>
-      <c r="F23" s="46"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="32"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="44"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="25">
+      <c r="A24" s="20">
         <v>45770</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="17">
         <v>0</v>
       </c>
       <c r="C24" s="7">
@@ -1573,17 +1613,17 @@
       <c r="E24" s="8">
         <v>0</v>
       </c>
-      <c r="F24" s="46"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="32"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="44"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="25">
+      <c r="A25" s="20">
         <v>45771</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="17">
         <v>0</v>
       </c>
       <c r="C25" s="7">
@@ -1595,17 +1635,17 @@
       <c r="E25" s="8">
         <v>0</v>
       </c>
-      <c r="F25" s="46"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="32"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="44"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="25">
+      <c r="A26" s="20">
         <v>45772</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="17">
         <v>0</v>
       </c>
       <c r="C26" s="7">
@@ -1614,20 +1654,24 @@
       <c r="D26" s="7">
         <v>0</v>
       </c>
-      <c r="E26" s="12">
-        <v>1</v>
-      </c>
-      <c r="F26" s="45"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="31"/>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="43"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="25">
+      <c r="A27" s="20">
         <v>45773</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="17">
         <v>0</v>
       </c>
       <c r="C27" s="7">
@@ -1636,20 +1680,26 @@
       <c r="D27" s="7">
         <v>0</v>
       </c>
-      <c r="E27" s="12">
-        <v>1</v>
-      </c>
-      <c r="F27" s="45"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="31"/>
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="14"/>
+      <c r="J27" s="43"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="25">
+      <c r="A28" s="20">
         <v>45774</v>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="17">
         <v>0</v>
       </c>
       <c r="C28" s="7">
@@ -1658,20 +1708,26 @@
       <c r="D28" s="7">
         <v>0</v>
       </c>
-      <c r="E28" s="12">
-        <v>1</v>
-      </c>
-      <c r="F28" s="45"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="31"/>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="14"/>
+      <c r="J28" s="43"/>
     </row>
     <row r="29" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25">
+      <c r="A29" s="20">
         <v>45775</v>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="17">
         <v>0</v>
       </c>
       <c r="C29" s="7">
@@ -1683,17 +1739,17 @@
       <c r="E29" s="8">
         <v>0</v>
       </c>
-      <c r="F29" s="46"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="31"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="43"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="25">
+      <c r="A30" s="20">
         <v>45776</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="17">
         <v>0</v>
       </c>
       <c r="C30" s="7">
@@ -1705,17 +1761,17 @@
       <c r="E30" s="8">
         <v>0</v>
       </c>
-      <c r="F30" s="46"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="31"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="43"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="25">
+      <c r="A31" s="20">
         <v>45777</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="17">
         <v>0</v>
       </c>
       <c r="C31" s="7">
@@ -1727,17 +1783,17 @@
       <c r="E31" s="8">
         <v>0</v>
       </c>
-      <c r="F31" s="46"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="31"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="43"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="25">
+      <c r="A32" s="20">
         <v>45778</v>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="17">
         <v>0</v>
       </c>
       <c r="C32" s="7">
@@ -1749,17 +1805,17 @@
       <c r="E32" s="8">
         <v>0</v>
       </c>
-      <c r="F32" s="46"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="32"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="44"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="25">
+      <c r="A33" s="20">
         <v>45779</v>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="17">
         <v>0</v>
       </c>
       <c r="C33" s="7">
@@ -1771,17 +1827,17 @@
       <c r="E33" s="8">
         <v>0</v>
       </c>
-      <c r="F33" s="46"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="32"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="44"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="25">
+      <c r="A34" s="20">
         <v>45780</v>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="16">
         <v>1</v>
       </c>
       <c r="C34" s="7">
@@ -1793,17 +1849,21 @@
       <c r="E34" s="8">
         <v>0</v>
       </c>
-      <c r="F34" s="48"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="31"/>
+      <c r="F34" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="43"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="25">
+      <c r="A35" s="20">
         <v>45781</v>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="16">
         <v>1</v>
       </c>
       <c r="C35" s="7">
@@ -1815,17 +1875,21 @@
       <c r="E35" s="8">
         <v>0</v>
       </c>
-      <c r="F35" s="48"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="31"/>
+      <c r="F35" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="43"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="25">
+      <c r="A36" s="20">
         <v>45782</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="16">
         <v>1</v>
       </c>
       <c r="C36" s="7">
@@ -1837,17 +1901,21 @@
       <c r="E36" s="8">
         <v>0</v>
       </c>
-      <c r="F36" s="45"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="31"/>
+      <c r="F36" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="43"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="25">
+      <c r="A37" s="20">
         <v>45783</v>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="17">
         <v>0</v>
       </c>
       <c r="C37" s="7">
@@ -1859,17 +1927,17 @@
       <c r="E37" s="8">
         <v>0</v>
       </c>
-      <c r="F37" s="46"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="31"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="43"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="25">
+      <c r="A38" s="20">
         <v>45784</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="17">
         <v>0</v>
       </c>
       <c r="C38" s="7">
@@ -1881,17 +1949,17 @@
       <c r="E38" s="8">
         <v>0</v>
       </c>
-      <c r="F38" s="46"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="31"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="43"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="25">
+      <c r="A39" s="20">
         <v>45785</v>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="17">
         <v>0</v>
       </c>
       <c r="C39" s="7">
@@ -1903,17 +1971,17 @@
       <c r="E39" s="8">
         <v>0</v>
       </c>
-      <c r="F39" s="46"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="31"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="43"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="25">
+      <c r="A40" s="20">
         <v>45786</v>
       </c>
-      <c r="B40" s="22">
+      <c r="B40" s="17">
         <v>0</v>
       </c>
       <c r="C40" s="7">
@@ -1925,17 +1993,17 @@
       <c r="E40" s="8">
         <v>0</v>
       </c>
-      <c r="F40" s="46"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="31"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="43"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="25">
+      <c r="A41" s="20">
         <v>45787</v>
       </c>
-      <c r="B41" s="22">
+      <c r="B41" s="17">
         <v>0</v>
       </c>
       <c r="C41" s="7">
@@ -1947,20 +2015,20 @@
       <c r="E41" s="8">
         <v>0</v>
       </c>
-      <c r="F41" s="46"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="32"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="44"/>
     </row>
     <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="25">
+      <c r="A42" s="20">
         <v>45788</v>
       </c>
-      <c r="B42" s="22">
-        <v>0</v>
-      </c>
-      <c r="C42" s="11">
+      <c r="B42" s="17">
+        <v>0</v>
+      </c>
+      <c r="C42" s="9">
         <v>1</v>
       </c>
       <c r="D42" s="7">
@@ -1969,20 +2037,22 @@
       <c r="E42" s="8">
         <v>0</v>
       </c>
-      <c r="F42" s="45"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="31"/>
+      <c r="F42" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="31"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="43"/>
     </row>
     <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="25">
+      <c r="A43" s="20">
         <v>45789</v>
       </c>
-      <c r="B43" s="22">
-        <v>0</v>
-      </c>
-      <c r="C43" s="11">
+      <c r="B43" s="17">
+        <v>0</v>
+      </c>
+      <c r="C43" s="9">
         <v>1</v>
       </c>
       <c r="D43" s="7">
@@ -1991,20 +2061,24 @@
       <c r="E43" s="8">
         <v>0</v>
       </c>
-      <c r="F43" s="45"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="31"/>
+      <c r="F43" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="43"/>
     </row>
     <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="25">
+      <c r="A44" s="20">
         <v>45790</v>
       </c>
-      <c r="B44" s="22">
-        <v>0</v>
-      </c>
-      <c r="C44" s="11">
+      <c r="B44" s="17">
+        <v>0</v>
+      </c>
+      <c r="C44" s="9">
         <v>1</v>
       </c>
       <c r="D44" s="7">
@@ -2013,17 +2087,21 @@
       <c r="E44" s="8">
         <v>0</v>
       </c>
-      <c r="F44" s="45"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="31"/>
+      <c r="F44" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="43"/>
     </row>
     <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="25">
+      <c r="A45" s="20">
         <v>45791</v>
       </c>
-      <c r="B45" s="22">
+      <c r="B45" s="17">
         <v>0</v>
       </c>
       <c r="C45" s="7">
@@ -2035,17 +2113,17 @@
       <c r="E45" s="8">
         <v>0</v>
       </c>
-      <c r="F45" s="46"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="32"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="44"/>
     </row>
     <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="25">
+      <c r="A46" s="20">
         <v>45792</v>
       </c>
-      <c r="B46" s="22">
+      <c r="B46" s="17">
         <v>0</v>
       </c>
       <c r="C46" s="7">
@@ -2057,17 +2135,17 @@
       <c r="E46" s="8">
         <v>0</v>
       </c>
-      <c r="F46" s="46"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="32"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="44"/>
     </row>
     <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="25">
+      <c r="A47" s="20">
         <v>45793</v>
       </c>
-      <c r="B47" s="22">
+      <c r="B47" s="17">
         <v>0</v>
       </c>
       <c r="C47" s="7">
@@ -2079,17 +2157,17 @@
       <c r="E47" s="8">
         <v>0</v>
       </c>
-      <c r="F47" s="46"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="31"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="43"/>
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="25">
+      <c r="A48" s="20">
         <v>45794</v>
       </c>
-      <c r="B48" s="22">
+      <c r="B48" s="17">
         <v>0</v>
       </c>
       <c r="C48" s="7">
@@ -2101,17 +2179,17 @@
       <c r="E48" s="8">
         <v>0</v>
       </c>
-      <c r="F48" s="46"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="31"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="43"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="25">
+      <c r="A49" s="20">
         <v>45795</v>
       </c>
-      <c r="B49" s="22">
+      <c r="B49" s="17">
         <v>0</v>
       </c>
       <c r="C49" s="7">
@@ -2123,83 +2201,93 @@
       <c r="E49" s="8">
         <v>0</v>
       </c>
-      <c r="F49" s="46"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="31"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="43"/>
     </row>
     <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="25">
+      <c r="A50" s="20">
         <v>45796</v>
       </c>
-      <c r="B50" s="22">
+      <c r="B50" s="17">
         <v>0</v>
       </c>
       <c r="C50" s="7">
         <v>0</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="9">
         <v>1</v>
       </c>
       <c r="E50" s="8">
         <v>0</v>
       </c>
-      <c r="F50" s="45"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="32"/>
+      <c r="F50" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="44"/>
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="25">
+      <c r="A51" s="20">
         <v>45797</v>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="17">
         <v>0</v>
       </c>
       <c r="C51" s="7">
         <v>0</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="9">
         <v>1</v>
       </c>
       <c r="E51" s="8">
         <v>0</v>
       </c>
-      <c r="F51" s="45"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="32"/>
+      <c r="F51" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="31"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="44"/>
     </row>
     <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="25">
+      <c r="A52" s="20">
         <v>45798</v>
       </c>
-      <c r="B52" s="22">
+      <c r="B52" s="17">
         <v>0</v>
       </c>
       <c r="C52" s="7">
         <v>0</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="9">
         <v>1</v>
       </c>
       <c r="E52" s="8">
         <v>0</v>
       </c>
-      <c r="F52" s="45"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="32"/>
+      <c r="F52" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="44"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="25">
+      <c r="A53" s="20">
         <v>45799</v>
       </c>
-      <c r="B53" s="22">
+      <c r="B53" s="17">
         <v>0</v>
       </c>
       <c r="C53" s="7">
@@ -2211,17 +2299,17 @@
       <c r="E53" s="8">
         <v>0</v>
       </c>
-      <c r="F53" s="46"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="32"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="44"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="25">
+      <c r="A54" s="20">
         <v>45800</v>
       </c>
-      <c r="B54" s="22">
+      <c r="B54" s="17">
         <v>0</v>
       </c>
       <c r="C54" s="7">
@@ -2233,17 +2321,17 @@
       <c r="E54" s="8">
         <v>0</v>
       </c>
-      <c r="F54" s="46"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="32"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="44"/>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="25">
+      <c r="A55" s="20">
         <v>45801</v>
       </c>
-      <c r="B55" s="22">
+      <c r="B55" s="17">
         <v>0</v>
       </c>
       <c r="C55" s="7">
@@ -2255,17 +2343,17 @@
       <c r="E55" s="8">
         <v>0</v>
       </c>
-      <c r="F55" s="46"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="32"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="44"/>
     </row>
     <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="25">
+      <c r="A56" s="20">
         <v>45802</v>
       </c>
-      <c r="B56" s="22">
+      <c r="B56" s="17">
         <v>0</v>
       </c>
       <c r="C56" s="7">
@@ -2277,17 +2365,17 @@
       <c r="E56" s="8">
         <v>0</v>
       </c>
-      <c r="F56" s="46"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="31"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="43"/>
     </row>
     <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="25">
+      <c r="A57" s="20">
         <v>45803</v>
       </c>
-      <c r="B57" s="22">
+      <c r="B57" s="17">
         <v>0</v>
       </c>
       <c r="C57" s="7">
@@ -2299,17 +2387,17 @@
       <c r="E57" s="8">
         <v>0</v>
       </c>
-      <c r="F57" s="46"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="31"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="43"/>
     </row>
     <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="25">
+      <c r="A58" s="20">
         <v>45804</v>
       </c>
-      <c r="B58" s="22">
+      <c r="B58" s="17">
         <v>0</v>
       </c>
       <c r="C58" s="7">
@@ -2318,20 +2406,24 @@
       <c r="D58" s="7">
         <v>0</v>
       </c>
-      <c r="E58" s="12">
-        <v>1</v>
-      </c>
-      <c r="F58" s="48"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="31"/>
+      <c r="E58" s="10">
+        <v>1</v>
+      </c>
+      <c r="F58" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="43"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="25">
+      <c r="A59" s="20">
         <v>45805</v>
       </c>
-      <c r="B59" s="22">
+      <c r="B59" s="17">
         <v>0</v>
       </c>
       <c r="C59" s="7">
@@ -2340,20 +2432,24 @@
       <c r="D59" s="7">
         <v>0</v>
       </c>
-      <c r="E59" s="12">
-        <v>1</v>
-      </c>
-      <c r="F59" s="48"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="31"/>
+      <c r="E59" s="10">
+        <v>1</v>
+      </c>
+      <c r="F59" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="43"/>
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="25">
+      <c r="A60" s="20">
         <v>45806</v>
       </c>
-      <c r="B60" s="22">
+      <c r="B60" s="17">
         <v>0</v>
       </c>
       <c r="C60" s="7">
@@ -2362,20 +2458,22 @@
       <c r="D60" s="7">
         <v>0</v>
       </c>
-      <c r="E60" s="12">
-        <v>1</v>
-      </c>
-      <c r="F60" s="45"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="31"/>
+      <c r="E60" s="10">
+        <v>1</v>
+      </c>
+      <c r="F60" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="31"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="43"/>
     </row>
     <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="25">
+      <c r="A61" s="20">
         <v>45807</v>
       </c>
-      <c r="B61" s="22">
+      <c r="B61" s="17">
         <v>0</v>
       </c>
       <c r="C61" s="7">
@@ -2387,17 +2485,17 @@
       <c r="E61" s="8">
         <v>0</v>
       </c>
-      <c r="F61" s="46"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="32"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="44"/>
     </row>
     <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="25">
+      <c r="A62" s="20">
         <v>45808</v>
       </c>
-      <c r="B62" s="22">
+      <c r="B62" s="17">
         <v>0</v>
       </c>
       <c r="C62" s="7">
@@ -2409,17 +2507,17 @@
       <c r="E62" s="8">
         <v>0</v>
       </c>
-      <c r="F62" s="46"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="32"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="44"/>
     </row>
     <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="25">
+      <c r="A63" s="20">
         <v>45809</v>
       </c>
-      <c r="B63" s="22">
+      <c r="B63" s="17">
         <v>0</v>
       </c>
       <c r="C63" s="7">
@@ -2431,17 +2529,17 @@
       <c r="E63" s="8">
         <v>0</v>
       </c>
-      <c r="F63" s="46"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="32"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="31"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="44"/>
     </row>
     <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="25">
+      <c r="A64" s="20">
         <v>45810</v>
       </c>
-      <c r="B64" s="22">
+      <c r="B64" s="17">
         <v>0</v>
       </c>
       <c r="C64" s="7">
@@ -2453,17 +2551,17 @@
       <c r="E64" s="8">
         <v>0</v>
       </c>
-      <c r="F64" s="46"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="32"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="44"/>
     </row>
     <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="25">
+      <c r="A65" s="20">
         <v>45811</v>
       </c>
-      <c r="B65" s="21">
+      <c r="B65" s="16">
         <v>1</v>
       </c>
       <c r="C65" s="7">
@@ -2475,17 +2573,19 @@
       <c r="E65" s="8">
         <v>0</v>
       </c>
-      <c r="F65" s="48"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="31"/>
+      <c r="F65" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="31"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="43"/>
     </row>
     <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="25">
+      <c r="A66" s="20">
         <v>45812</v>
       </c>
-      <c r="B66" s="21">
+      <c r="B66" s="16">
         <v>1</v>
       </c>
       <c r="C66" s="7">
@@ -2497,17 +2597,19 @@
       <c r="E66" s="8">
         <v>0</v>
       </c>
-      <c r="F66" s="48"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="31"/>
+      <c r="F66" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="31"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="43"/>
     </row>
     <row r="67" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="25">
+      <c r="A67" s="20">
         <v>45813</v>
       </c>
-      <c r="B67" s="21">
+      <c r="B67" s="16">
         <v>1</v>
       </c>
       <c r="C67" s="7">
@@ -2519,17 +2621,21 @@
       <c r="E67" s="8">
         <v>0</v>
       </c>
-      <c r="F67" s="45"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="31"/>
+      <c r="F67" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="43"/>
     </row>
     <row r="68" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="25">
+      <c r="A68" s="20">
         <v>45814</v>
       </c>
-      <c r="B68" s="22">
+      <c r="B68" s="17">
         <v>0</v>
       </c>
       <c r="C68" s="7">
@@ -2541,17 +2647,17 @@
       <c r="E68" s="8">
         <v>0</v>
       </c>
-      <c r="F68" s="46"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="32"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="44"/>
     </row>
     <row r="69" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="25">
+      <c r="A69" s="20">
         <v>45815</v>
       </c>
-      <c r="B69" s="22">
+      <c r="B69" s="17">
         <v>0</v>
       </c>
       <c r="C69" s="7">
@@ -2563,17 +2669,17 @@
       <c r="E69" s="8">
         <v>0</v>
       </c>
-      <c r="F69" s="46"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="32"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="44"/>
     </row>
     <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="25">
+      <c r="A70" s="20">
         <v>45816</v>
       </c>
-      <c r="B70" s="22">
+      <c r="B70" s="17">
         <v>0</v>
       </c>
       <c r="C70" s="7">
@@ -2585,17 +2691,17 @@
       <c r="E70" s="8">
         <v>0</v>
       </c>
-      <c r="F70" s="46"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="32"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="44"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="25">
+      <c r="A71" s="20">
         <v>45817</v>
       </c>
-      <c r="B71" s="22">
+      <c r="B71" s="17">
         <v>0</v>
       </c>
       <c r="C71" s="7">
@@ -2607,17 +2713,17 @@
       <c r="E71" s="8">
         <v>0</v>
       </c>
-      <c r="F71" s="46"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="32"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="44"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="25">
+      <c r="A72" s="20">
         <v>45818</v>
       </c>
-      <c r="B72" s="22">
+      <c r="B72" s="17">
         <v>0</v>
       </c>
       <c r="C72" s="7">
@@ -2629,20 +2735,20 @@
       <c r="E72" s="8">
         <v>0</v>
       </c>
-      <c r="F72" s="46"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="32"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="44"/>
     </row>
     <row r="73" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="25">
+      <c r="A73" s="20">
         <v>45819</v>
       </c>
-      <c r="B73" s="22">
-        <v>0</v>
-      </c>
-      <c r="C73" s="11">
+      <c r="B73" s="17">
+        <v>0</v>
+      </c>
+      <c r="C73" s="9">
         <v>1</v>
       </c>
       <c r="D73" s="7">
@@ -2651,20 +2757,22 @@
       <c r="E73" s="8">
         <v>0</v>
       </c>
-      <c r="F73" s="45"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="31"/>
+      <c r="F73" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="31"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="43"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="25">
+      <c r="A74" s="20">
         <v>45820</v>
       </c>
-      <c r="B74" s="22">
-        <v>0</v>
-      </c>
-      <c r="C74" s="11">
+      <c r="B74" s="17">
+        <v>0</v>
+      </c>
+      <c r="C74" s="9">
         <v>1</v>
       </c>
       <c r="D74" s="7">
@@ -2673,20 +2781,24 @@
       <c r="E74" s="8">
         <v>0</v>
       </c>
-      <c r="F74" s="45"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="31"/>
+      <c r="F74" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="43"/>
     </row>
     <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="25">
+      <c r="A75" s="20">
         <v>45821</v>
       </c>
-      <c r="B75" s="22">
-        <v>0</v>
-      </c>
-      <c r="C75" s="11">
+      <c r="B75" s="17">
+        <v>0</v>
+      </c>
+      <c r="C75" s="9">
         <v>1</v>
       </c>
       <c r="D75" s="7">
@@ -2695,17 +2807,21 @@
       <c r="E75" s="8">
         <v>0</v>
       </c>
-      <c r="F75" s="45"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="31"/>
+      <c r="F75" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="43"/>
     </row>
     <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="25">
+      <c r="A76" s="20">
         <v>45822</v>
       </c>
-      <c r="B76" s="22">
+      <c r="B76" s="17">
         <v>0</v>
       </c>
       <c r="C76" s="7">
@@ -2717,17 +2833,17 @@
       <c r="E76" s="8">
         <v>0</v>
       </c>
-      <c r="F76" s="46"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="31"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="43"/>
     </row>
     <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="25">
+      <c r="A77" s="20">
         <v>45823</v>
       </c>
-      <c r="B77" s="22">
+      <c r="B77" s="17">
         <v>0</v>
       </c>
       <c r="C77" s="7">
@@ -2739,17 +2855,17 @@
       <c r="E77" s="8">
         <v>0</v>
       </c>
-      <c r="F77" s="46"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="32"/>
+      <c r="F77" s="36"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="44"/>
     </row>
     <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="25">
+      <c r="A78" s="20">
         <v>45824</v>
       </c>
-      <c r="B78" s="22">
+      <c r="B78" s="17">
         <v>0</v>
       </c>
       <c r="C78" s="7">
@@ -2761,17 +2877,17 @@
       <c r="E78" s="8">
         <v>0</v>
       </c>
-      <c r="F78" s="46"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="32"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="44"/>
     </row>
     <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="25">
+      <c r="A79" s="20">
         <v>45825</v>
       </c>
-      <c r="B79" s="22">
+      <c r="B79" s="17">
         <v>0</v>
       </c>
       <c r="C79" s="7">
@@ -2783,17 +2899,17 @@
       <c r="E79" s="8">
         <v>0</v>
       </c>
-      <c r="F79" s="46"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="32"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="44"/>
     </row>
     <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="25">
+      <c r="A80" s="20">
         <v>45826</v>
       </c>
-      <c r="B80" s="22">
+      <c r="B80" s="17">
         <v>0</v>
       </c>
       <c r="C80" s="7">
@@ -2805,83 +2921,93 @@
       <c r="E80" s="8">
         <v>0</v>
       </c>
-      <c r="F80" s="46"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="32"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="31"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="44"/>
     </row>
     <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="25">
+      <c r="A81" s="20">
         <v>45827</v>
       </c>
-      <c r="B81" s="22">
+      <c r="B81" s="17">
         <v>0</v>
       </c>
       <c r="C81" s="7">
         <v>0</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="9">
         <v>1</v>
       </c>
       <c r="E81" s="8">
         <v>0</v>
       </c>
-      <c r="F81" s="48"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="31"/>
+      <c r="F81" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="43"/>
     </row>
     <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="25">
+      <c r="A82" s="20">
         <v>45828</v>
       </c>
-      <c r="B82" s="22">
+      <c r="B82" s="17">
         <v>0</v>
       </c>
       <c r="C82" s="7">
         <v>0</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="9">
         <v>1</v>
       </c>
       <c r="E82" s="8">
         <v>0</v>
       </c>
-      <c r="F82" s="48"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="32"/>
+      <c r="F82" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="44"/>
     </row>
     <row r="83" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="25">
+      <c r="A83" s="20">
         <v>45829</v>
       </c>
-      <c r="B83" s="22">
+      <c r="B83" s="17">
         <v>0</v>
       </c>
       <c r="C83" s="7">
         <v>0</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="9">
         <v>1</v>
       </c>
       <c r="E83" s="8">
         <v>0</v>
       </c>
-      <c r="F83" s="45"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="31"/>
+      <c r="F83" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" s="31"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="43"/>
     </row>
     <row r="84" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="25">
+      <c r="A84" s="20">
         <v>45830</v>
       </c>
-      <c r="B84" s="22">
+      <c r="B84" s="17">
         <v>0</v>
       </c>
       <c r="C84" s="7">
@@ -2893,17 +3019,17 @@
       <c r="E84" s="8">
         <v>0</v>
       </c>
-      <c r="F84" s="46"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="31"/>
+      <c r="F84" s="36"/>
+      <c r="G84" s="31"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="43"/>
     </row>
     <row r="85" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="25">
+      <c r="A85" s="20">
         <v>45831</v>
       </c>
-      <c r="B85" s="22">
+      <c r="B85" s="17">
         <v>0</v>
       </c>
       <c r="C85" s="7">
@@ -2915,17 +3041,17 @@
       <c r="E85" s="8">
         <v>0</v>
       </c>
-      <c r="F85" s="46"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="31"/>
+      <c r="F85" s="36"/>
+      <c r="G85" s="31"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="43"/>
     </row>
     <row r="86" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="25">
+      <c r="A86" s="20">
         <v>45832</v>
       </c>
-      <c r="B86" s="22">
+      <c r="B86" s="17">
         <v>0</v>
       </c>
       <c r="C86" s="7">
@@ -2937,17 +3063,17 @@
       <c r="E86" s="8">
         <v>0</v>
       </c>
-      <c r="F86" s="46"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="32"/>
+      <c r="F86" s="36"/>
+      <c r="G86" s="31"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="44"/>
     </row>
     <row r="87" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="20">
         <v>45833</v>
       </c>
-      <c r="B87" s="22">
+      <c r="B87" s="17">
         <v>0</v>
       </c>
       <c r="C87" s="7">
@@ -2959,17 +3085,17 @@
       <c r="E87" s="8">
         <v>0</v>
       </c>
-      <c r="F87" s="46"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="32"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="31"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="44"/>
     </row>
     <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="25">
+      <c r="A88" s="20">
         <v>45834</v>
       </c>
-      <c r="B88" s="22">
+      <c r="B88" s="17">
         <v>0</v>
       </c>
       <c r="C88" s="7">
@@ -2981,17 +3107,17 @@
       <c r="E88" s="8">
         <v>0</v>
       </c>
-      <c r="F88" s="46"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="10"/>
-      <c r="J88" s="32"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="31"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="44"/>
     </row>
     <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="25">
+      <c r="A89" s="20">
         <v>45835</v>
       </c>
-      <c r="B89" s="22">
+      <c r="B89" s="17">
         <v>0</v>
       </c>
       <c r="C89" s="7">
@@ -3000,20 +3126,24 @@
       <c r="D89" s="7">
         <v>0</v>
       </c>
-      <c r="E89" s="12">
-        <v>1</v>
-      </c>
-      <c r="F89" s="45"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="31"/>
+      <c r="E89" s="10">
+        <v>1</v>
+      </c>
+      <c r="F89" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="43"/>
     </row>
     <row r="90" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="25">
+      <c r="A90" s="20">
         <v>45836</v>
       </c>
-      <c r="B90" s="22">
+      <c r="B90" s="17">
         <v>0</v>
       </c>
       <c r="C90" s="7">
@@ -3022,20 +3152,22 @@
       <c r="D90" s="7">
         <v>0</v>
       </c>
-      <c r="E90" s="12">
-        <v>1</v>
-      </c>
-      <c r="F90" s="45"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="10"/>
-      <c r="J90" s="31"/>
+      <c r="E90" s="10">
+        <v>1</v>
+      </c>
+      <c r="F90" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" s="31"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="43"/>
     </row>
     <row r="91" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="25">
+      <c r="A91" s="20">
         <v>45837</v>
       </c>
-      <c r="B91" s="22">
+      <c r="B91" s="17">
         <v>0</v>
       </c>
       <c r="C91" s="7">
@@ -3044,20 +3176,22 @@
       <c r="D91" s="7">
         <v>0</v>
       </c>
-      <c r="E91" s="12">
-        <v>1</v>
-      </c>
-      <c r="F91" s="45"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="31"/>
+      <c r="E91" s="10">
+        <v>1</v>
+      </c>
+      <c r="F91" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="31"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="43"/>
     </row>
     <row r="92" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="25">
+      <c r="A92" s="20">
         <v>45838</v>
       </c>
-      <c r="B92" s="22">
+      <c r="B92" s="17">
         <v>0</v>
       </c>
       <c r="C92" s="7">
@@ -3069,17 +3203,17 @@
       <c r="E92" s="8">
         <v>0</v>
       </c>
-      <c r="F92" s="46"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="32"/>
+      <c r="F92" s="36"/>
+      <c r="G92" s="31"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="44"/>
     </row>
     <row r="93" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="25">
+      <c r="A93" s="20">
         <v>45839</v>
       </c>
-      <c r="B93" s="22">
+      <c r="B93" s="17">
         <v>0</v>
       </c>
       <c r="C93" s="7">
@@ -3091,17 +3225,17 @@
       <c r="E93" s="8">
         <v>0</v>
       </c>
-      <c r="F93" s="46"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="32"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="31"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="44"/>
     </row>
     <row r="94" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="25">
+      <c r="A94" s="20">
         <v>45840</v>
       </c>
-      <c r="B94" s="22">
+      <c r="B94" s="17">
         <v>0</v>
       </c>
       <c r="C94" s="7">
@@ -3113,17 +3247,17 @@
       <c r="E94" s="8">
         <v>0</v>
       </c>
-      <c r="F94" s="46"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="32"/>
+      <c r="F94" s="36"/>
+      <c r="G94" s="31"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="44"/>
     </row>
     <row r="95" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="25">
+      <c r="A95" s="20">
         <v>45841</v>
       </c>
-      <c r="B95" s="22">
+      <c r="B95" s="17">
         <v>0</v>
       </c>
       <c r="C95" s="7">
@@ -3135,17 +3269,17 @@
       <c r="E95" s="8">
         <v>0</v>
       </c>
-      <c r="F95" s="46"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="9"/>
-      <c r="I95" s="10"/>
-      <c r="J95" s="32"/>
+      <c r="F95" s="36"/>
+      <c r="G95" s="31"/>
+      <c r="H95" s="14"/>
+      <c r="I95" s="14"/>
+      <c r="J95" s="44"/>
     </row>
     <row r="96" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="25">
+      <c r="A96" s="20">
         <v>45842</v>
       </c>
-      <c r="B96" s="22">
+      <c r="B96" s="17">
         <v>0</v>
       </c>
       <c r="C96" s="7">
@@ -3157,17 +3291,17 @@
       <c r="E96" s="8">
         <v>0</v>
       </c>
-      <c r="F96" s="46"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="32"/>
+      <c r="F96" s="36"/>
+      <c r="G96" s="31"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="44"/>
     </row>
     <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="25">
+      <c r="A97" s="20">
         <v>45843</v>
       </c>
-      <c r="B97" s="21">
+      <c r="B97" s="16">
         <v>1</v>
       </c>
       <c r="C97" s="7">
@@ -3179,17 +3313,19 @@
       <c r="E97" s="8">
         <v>0</v>
       </c>
-      <c r="F97" s="48"/>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="10"/>
-      <c r="J97" s="31"/>
+      <c r="F97" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" s="31"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="43"/>
     </row>
     <row r="98" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="25">
+      <c r="A98" s="20">
         <v>45844</v>
       </c>
-      <c r="B98" s="21">
+      <c r="B98" s="16">
         <v>1</v>
       </c>
       <c r="C98" s="7">
@@ -3201,17 +3337,21 @@
       <c r="E98" s="8">
         <v>0</v>
       </c>
-      <c r="F98" s="48"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="10"/>
-      <c r="J98" s="31"/>
+      <c r="F98" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" s="14"/>
+      <c r="I98" s="14"/>
+      <c r="J98" s="43"/>
     </row>
     <row r="99" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="25">
+      <c r="A99" s="20">
         <v>45845</v>
       </c>
-      <c r="B99" s="21">
+      <c r="B99" s="16">
         <v>1</v>
       </c>
       <c r="C99" s="7">
@@ -3223,17 +3363,21 @@
       <c r="E99" s="8">
         <v>0</v>
       </c>
-      <c r="F99" s="45"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="31"/>
+      <c r="F99" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" s="14"/>
+      <c r="I99" s="14"/>
+      <c r="J99" s="43"/>
     </row>
     <row r="100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="25">
+      <c r="A100" s="20">
         <v>45846</v>
       </c>
-      <c r="B100" s="22">
+      <c r="B100" s="17">
         <v>0</v>
       </c>
       <c r="C100" s="7">
@@ -3245,17 +3389,17 @@
       <c r="E100" s="8">
         <v>0</v>
       </c>
-      <c r="F100" s="46"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="10"/>
-      <c r="J100" s="32"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="14"/>
+      <c r="I100" s="14"/>
+      <c r="J100" s="44"/>
     </row>
     <row r="101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="25">
+      <c r="A101" s="20">
         <v>45847</v>
       </c>
-      <c r="B101" s="22">
+      <c r="B101" s="17">
         <v>0</v>
       </c>
       <c r="C101" s="7">
@@ -3267,17 +3411,17 @@
       <c r="E101" s="8">
         <v>0</v>
       </c>
-      <c r="F101" s="46"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
-      <c r="I101" s="10"/>
-      <c r="J101" s="32"/>
+      <c r="F101" s="36"/>
+      <c r="G101" s="31"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="44"/>
     </row>
     <row r="102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="25">
+      <c r="A102" s="20">
         <v>45848</v>
       </c>
-      <c r="B102" s="22">
+      <c r="B102" s="17">
         <v>0</v>
       </c>
       <c r="C102" s="7">
@@ -3289,17 +3433,17 @@
       <c r="E102" s="8">
         <v>0</v>
       </c>
-      <c r="F102" s="46"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
-      <c r="I102" s="10"/>
-      <c r="J102" s="32"/>
+      <c r="F102" s="36"/>
+      <c r="G102" s="31"/>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
+      <c r="J102" s="44"/>
     </row>
     <row r="103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="25">
+      <c r="A103" s="20">
         <v>45849</v>
       </c>
-      <c r="B103" s="22">
+      <c r="B103" s="17">
         <v>0</v>
       </c>
       <c r="C103" s="7">
@@ -3311,17 +3455,17 @@
       <c r="E103" s="8">
         <v>0</v>
       </c>
-      <c r="F103" s="46"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="10"/>
-      <c r="J103" s="32"/>
+      <c r="F103" s="36"/>
+      <c r="G103" s="31"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="44"/>
     </row>
     <row r="104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="25">
+      <c r="A104" s="20">
         <v>45850</v>
       </c>
-      <c r="B104" s="22">
+      <c r="B104" s="17">
         <v>0</v>
       </c>
       <c r="C104" s="7">
@@ -3333,20 +3477,20 @@
       <c r="E104" s="8">
         <v>0</v>
       </c>
-      <c r="F104" s="46"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="10"/>
-      <c r="J104" s="32"/>
+      <c r="F104" s="36"/>
+      <c r="G104" s="31"/>
+      <c r="H104" s="14"/>
+      <c r="I104" s="14"/>
+      <c r="J104" s="44"/>
     </row>
     <row r="105" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="25">
+      <c r="A105" s="20">
         <v>45851</v>
       </c>
-      <c r="B105" s="22">
-        <v>0</v>
-      </c>
-      <c r="C105" s="11">
+      <c r="B105" s="17">
+        <v>0</v>
+      </c>
+      <c r="C105" s="9">
         <v>1</v>
       </c>
       <c r="D105" s="7">
@@ -3355,20 +3499,24 @@
       <c r="E105" s="8">
         <v>0</v>
       </c>
-      <c r="F105" s="45"/>
-      <c r="G105" s="9"/>
-      <c r="H105" s="9"/>
-      <c r="I105" s="10"/>
-      <c r="J105" s="31"/>
+      <c r="F105" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" s="14"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="43"/>
     </row>
     <row r="106" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="25">
+      <c r="A106" s="20">
         <v>45852</v>
       </c>
-      <c r="B106" s="22">
-        <v>0</v>
-      </c>
-      <c r="C106" s="11">
+      <c r="B106" s="17">
+        <v>0</v>
+      </c>
+      <c r="C106" s="9">
         <v>1</v>
       </c>
       <c r="D106" s="7">
@@ -3377,20 +3525,24 @@
       <c r="E106" s="8">
         <v>0</v>
       </c>
-      <c r="F106" s="45"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="10"/>
-      <c r="J106" s="31"/>
+      <c r="F106" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" s="14"/>
+      <c r="I106" s="14"/>
+      <c r="J106" s="43"/>
     </row>
     <row r="107" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="25">
+      <c r="A107" s="20">
         <v>45853</v>
       </c>
-      <c r="B107" s="22">
-        <v>0</v>
-      </c>
-      <c r="C107" s="11">
+      <c r="B107" s="17">
+        <v>0</v>
+      </c>
+      <c r="C107" s="9">
         <v>1</v>
       </c>
       <c r="D107" s="7">
@@ -3399,17 +3551,19 @@
       <c r="E107" s="8">
         <v>0</v>
       </c>
-      <c r="F107" s="45"/>
-      <c r="G107" s="9"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="10"/>
-      <c r="J107" s="31"/>
+      <c r="F107" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107" s="31"/>
+      <c r="H107" s="14"/>
+      <c r="I107" s="14"/>
+      <c r="J107" s="43"/>
     </row>
     <row r="108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="25">
+      <c r="A108" s="20">
         <v>45854</v>
       </c>
-      <c r="B108" s="22">
+      <c r="B108" s="17">
         <v>0</v>
       </c>
       <c r="C108" s="7">
@@ -3421,17 +3575,17 @@
       <c r="E108" s="8">
         <v>0</v>
       </c>
-      <c r="F108" s="46"/>
-      <c r="G108" s="9"/>
-      <c r="H108" s="9"/>
-      <c r="I108" s="10"/>
-      <c r="J108" s="32"/>
+      <c r="F108" s="36"/>
+      <c r="G108" s="31"/>
+      <c r="H108" s="14"/>
+      <c r="I108" s="14"/>
+      <c r="J108" s="44"/>
     </row>
     <row r="109" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="25">
+      <c r="A109" s="20">
         <v>45855</v>
       </c>
-      <c r="B109" s="22">
+      <c r="B109" s="17">
         <v>0</v>
       </c>
       <c r="C109" s="7">
@@ -3443,17 +3597,17 @@
       <c r="E109" s="8">
         <v>0</v>
       </c>
-      <c r="F109" s="46"/>
-      <c r="G109" s="9"/>
-      <c r="H109" s="9"/>
-      <c r="I109" s="10"/>
-      <c r="J109" s="32"/>
+      <c r="F109" s="36"/>
+      <c r="G109" s="31"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="14"/>
+      <c r="J109" s="44"/>
     </row>
     <row r="110" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="25">
+      <c r="A110" s="20">
         <v>45856</v>
       </c>
-      <c r="B110" s="22">
+      <c r="B110" s="17">
         <v>0</v>
       </c>
       <c r="C110" s="7">
@@ -3465,17 +3619,17 @@
       <c r="E110" s="8">
         <v>0</v>
       </c>
-      <c r="F110" s="46"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="32"/>
+      <c r="F110" s="36"/>
+      <c r="G110" s="31"/>
+      <c r="H110" s="14"/>
+      <c r="I110" s="14"/>
+      <c r="J110" s="44"/>
     </row>
     <row r="111" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="25">
+      <c r="A111" s="20">
         <v>45857</v>
       </c>
-      <c r="B111" s="22">
+      <c r="B111" s="17">
         <v>0</v>
       </c>
       <c r="C111" s="7">
@@ -3487,17 +3641,17 @@
       <c r="E111" s="8">
         <v>0</v>
       </c>
-      <c r="F111" s="46"/>
-      <c r="G111" s="9"/>
-      <c r="H111" s="9"/>
-      <c r="I111" s="10"/>
-      <c r="J111" s="32"/>
+      <c r="F111" s="36"/>
+      <c r="G111" s="31"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="14"/>
+      <c r="J111" s="44"/>
     </row>
     <row r="112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="25">
+      <c r="A112" s="20">
         <v>45858</v>
       </c>
-      <c r="B112" s="22">
+      <c r="B112" s="17">
         <v>0</v>
       </c>
       <c r="C112" s="7">
@@ -3509,83 +3663,93 @@
       <c r="E112" s="8">
         <v>0</v>
       </c>
-      <c r="F112" s="46"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="10"/>
-      <c r="J112" s="32"/>
+      <c r="F112" s="36"/>
+      <c r="G112" s="31"/>
+      <c r="H112" s="14"/>
+      <c r="I112" s="14"/>
+      <c r="J112" s="44"/>
     </row>
     <row r="113" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="25">
+      <c r="A113" s="20">
         <v>45859</v>
       </c>
-      <c r="B113" s="22">
+      <c r="B113" s="17">
         <v>0</v>
       </c>
       <c r="C113" s="7">
         <v>0</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="9">
         <v>1</v>
       </c>
       <c r="E113" s="8">
         <v>0</v>
       </c>
-      <c r="F113" s="48"/>
-      <c r="G113" s="9"/>
-      <c r="H113" s="9"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="31"/>
+      <c r="F113" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H113" s="14"/>
+      <c r="I113" s="14"/>
+      <c r="J113" s="43"/>
     </row>
     <row r="114" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="25">
+      <c r="A114" s="20">
         <v>45860</v>
       </c>
-      <c r="B114" s="22">
+      <c r="B114" s="17">
         <v>0</v>
       </c>
       <c r="C114" s="7">
         <v>0</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D114" s="9">
         <v>1</v>
       </c>
       <c r="E114" s="8">
         <v>0</v>
       </c>
-      <c r="F114" s="48"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="9"/>
-      <c r="I114" s="10"/>
-      <c r="J114" s="31"/>
+      <c r="F114" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" s="14"/>
+      <c r="I114" s="14"/>
+      <c r="J114" s="43"/>
     </row>
     <row r="115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="25">
+      <c r="A115" s="20">
         <v>45861</v>
       </c>
-      <c r="B115" s="22">
+      <c r="B115" s="17">
         <v>0</v>
       </c>
       <c r="C115" s="7">
         <v>0</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="9">
         <v>1</v>
       </c>
       <c r="E115" s="8">
         <v>0</v>
       </c>
-      <c r="F115" s="45"/>
-      <c r="G115" s="9"/>
-      <c r="H115" s="9"/>
-      <c r="I115" s="10"/>
-      <c r="J115" s="31"/>
+      <c r="F115" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115" s="31"/>
+      <c r="H115" s="14"/>
+      <c r="I115" s="14"/>
+      <c r="J115" s="43"/>
     </row>
     <row r="116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="25">
+      <c r="A116" s="20">
         <v>45862</v>
       </c>
-      <c r="B116" s="22">
+      <c r="B116" s="17">
         <v>0</v>
       </c>
       <c r="C116" s="7">
@@ -3597,17 +3761,17 @@
       <c r="E116" s="8">
         <v>0</v>
       </c>
-      <c r="F116" s="46"/>
-      <c r="G116" s="9"/>
-      <c r="H116" s="9"/>
-      <c r="I116" s="10"/>
-      <c r="J116" s="32"/>
+      <c r="F116" s="36"/>
+      <c r="G116" s="31"/>
+      <c r="H116" s="14"/>
+      <c r="I116" s="14"/>
+      <c r="J116" s="44"/>
     </row>
     <row r="117" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="25">
+      <c r="A117" s="20">
         <v>45863</v>
       </c>
-      <c r="B117" s="22">
+      <c r="B117" s="17">
         <v>0</v>
       </c>
       <c r="C117" s="7">
@@ -3619,17 +3783,17 @@
       <c r="E117" s="8">
         <v>0</v>
       </c>
-      <c r="F117" s="46"/>
-      <c r="G117" s="9"/>
-      <c r="H117" s="9"/>
-      <c r="I117" s="10"/>
-      <c r="J117" s="32"/>
+      <c r="F117" s="36"/>
+      <c r="G117" s="31"/>
+      <c r="H117" s="14"/>
+      <c r="I117" s="14"/>
+      <c r="J117" s="44"/>
     </row>
     <row r="118" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="25">
+      <c r="A118" s="20">
         <v>45864</v>
       </c>
-      <c r="B118" s="22">
+      <c r="B118" s="17">
         <v>0</v>
       </c>
       <c r="C118" s="7">
@@ -3641,17 +3805,17 @@
       <c r="E118" s="8">
         <v>0</v>
       </c>
-      <c r="F118" s="46"/>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
-      <c r="I118" s="10"/>
-      <c r="J118" s="32"/>
+      <c r="F118" s="36"/>
+      <c r="G118" s="31"/>
+      <c r="H118" s="14"/>
+      <c r="I118" s="14"/>
+      <c r="J118" s="44"/>
     </row>
     <row r="119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="25">
+      <c r="A119" s="20">
         <v>45865</v>
       </c>
-      <c r="B119" s="22">
+      <c r="B119" s="17">
         <v>0</v>
       </c>
       <c r="C119" s="7">
@@ -3663,17 +3827,17 @@
       <c r="E119" s="8">
         <v>0</v>
       </c>
-      <c r="F119" s="46"/>
-      <c r="G119" s="9"/>
-      <c r="H119" s="9"/>
-      <c r="I119" s="10"/>
-      <c r="J119" s="32"/>
+      <c r="F119" s="36"/>
+      <c r="G119" s="31"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14"/>
+      <c r="J119" s="44"/>
     </row>
     <row r="120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="25">
+      <c r="A120" s="20">
         <v>45866</v>
       </c>
-      <c r="B120" s="22">
+      <c r="B120" s="17">
         <v>0</v>
       </c>
       <c r="C120" s="7">
@@ -3685,17 +3849,17 @@
       <c r="E120" s="8">
         <v>0</v>
       </c>
-      <c r="F120" s="46"/>
-      <c r="G120" s="9"/>
-      <c r="H120" s="9"/>
-      <c r="I120" s="10"/>
-      <c r="J120" s="32"/>
+      <c r="F120" s="36"/>
+      <c r="G120" s="31"/>
+      <c r="H120" s="14"/>
+      <c r="I120" s="14"/>
+      <c r="J120" s="44"/>
     </row>
     <row r="121" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="25">
+      <c r="A121" s="20">
         <v>45867</v>
       </c>
-      <c r="B121" s="22">
+      <c r="B121" s="17">
         <v>0</v>
       </c>
       <c r="C121" s="7">
@@ -3704,20 +3868,24 @@
       <c r="D121" s="7">
         <v>0</v>
       </c>
-      <c r="E121" s="12">
-        <v>1</v>
-      </c>
-      <c r="F121" s="45"/>
-      <c r="G121" s="9"/>
-      <c r="H121" s="9"/>
-      <c r="I121" s="10"/>
-      <c r="J121" s="31"/>
+      <c r="E121" s="10">
+        <v>1</v>
+      </c>
+      <c r="F121" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H121" s="14"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="43"/>
     </row>
     <row r="122" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="25">
+      <c r="A122" s="20">
         <v>45868</v>
       </c>
-      <c r="B122" s="22">
+      <c r="B122" s="17">
         <v>0</v>
       </c>
       <c r="C122" s="7">
@@ -3726,20 +3894,22 @@
       <c r="D122" s="7">
         <v>0</v>
       </c>
-      <c r="E122" s="12">
-        <v>1</v>
-      </c>
-      <c r="F122" s="45"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
-      <c r="I122" s="10"/>
-      <c r="J122" s="31"/>
+      <c r="E122" s="10">
+        <v>1</v>
+      </c>
+      <c r="F122" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G122" s="31"/>
+      <c r="H122" s="14"/>
+      <c r="I122" s="14"/>
+      <c r="J122" s="43"/>
     </row>
     <row r="123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="25">
+      <c r="A123" s="20">
         <v>45869</v>
       </c>
-      <c r="B123" s="22">
+      <c r="B123" s="17">
         <v>0</v>
       </c>
       <c r="C123" s="7">
@@ -3748,20 +3918,22 @@
       <c r="D123" s="7">
         <v>0</v>
       </c>
-      <c r="E123" s="12">
-        <v>1</v>
-      </c>
-      <c r="F123" s="45"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
-      <c r="I123" s="10"/>
-      <c r="J123" s="31"/>
+      <c r="E123" s="10">
+        <v>1</v>
+      </c>
+      <c r="F123" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G123" s="31"/>
+      <c r="H123" s="14"/>
+      <c r="I123" s="14"/>
+      <c r="J123" s="43"/>
     </row>
     <row r="124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="25">
+      <c r="A124" s="20">
         <v>45870</v>
       </c>
-      <c r="B124" s="22">
+      <c r="B124" s="17">
         <v>0</v>
       </c>
       <c r="C124" s="7">
@@ -3773,17 +3945,17 @@
       <c r="E124" s="8">
         <v>0</v>
       </c>
-      <c r="F124" s="46"/>
-      <c r="G124" s="9"/>
-      <c r="H124" s="9"/>
-      <c r="I124" s="10"/>
-      <c r="J124" s="32"/>
+      <c r="F124" s="36"/>
+      <c r="G124" s="31"/>
+      <c r="H124" s="14"/>
+      <c r="I124" s="14"/>
+      <c r="J124" s="44"/>
     </row>
     <row r="125" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="25">
+      <c r="A125" s="20">
         <v>45871</v>
       </c>
-      <c r="B125" s="22">
+      <c r="B125" s="17">
         <v>0</v>
       </c>
       <c r="C125" s="7">
@@ -3795,17 +3967,17 @@
       <c r="E125" s="8">
         <v>0</v>
       </c>
-      <c r="F125" s="46"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="9"/>
-      <c r="I125" s="10"/>
-      <c r="J125" s="32"/>
+      <c r="F125" s="36"/>
+      <c r="G125" s="31"/>
+      <c r="H125" s="14"/>
+      <c r="I125" s="14"/>
+      <c r="J125" s="44"/>
     </row>
     <row r="126" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="25">
+      <c r="A126" s="20">
         <v>45872</v>
       </c>
-      <c r="B126" s="22">
+      <c r="B126" s="17">
         <v>0</v>
       </c>
       <c r="C126" s="7">
@@ -3817,17 +3989,17 @@
       <c r="E126" s="8">
         <v>0</v>
       </c>
-      <c r="F126" s="46"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="9"/>
-      <c r="I126" s="10"/>
-      <c r="J126" s="32"/>
+      <c r="F126" s="36"/>
+      <c r="G126" s="31"/>
+      <c r="H126" s="14"/>
+      <c r="I126" s="14"/>
+      <c r="J126" s="44"/>
     </row>
     <row r="127" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="25">
+      <c r="A127" s="20">
         <v>45873</v>
       </c>
-      <c r="B127" s="22">
+      <c r="B127" s="17">
         <v>0</v>
       </c>
       <c r="C127" s="7">
@@ -3839,17 +4011,17 @@
       <c r="E127" s="8">
         <v>0</v>
       </c>
-      <c r="F127" s="46"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="9"/>
-      <c r="I127" s="10"/>
-      <c r="J127" s="32"/>
+      <c r="F127" s="36"/>
+      <c r="G127" s="31"/>
+      <c r="H127" s="14"/>
+      <c r="I127" s="14"/>
+      <c r="J127" s="44"/>
     </row>
     <row r="128" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="25">
+      <c r="A128" s="20">
         <v>45874</v>
       </c>
-      <c r="B128" s="22">
+      <c r="B128" s="17">
         <v>0</v>
       </c>
       <c r="C128" s="7">
@@ -3861,17 +4033,17 @@
       <c r="E128" s="8">
         <v>0</v>
       </c>
-      <c r="F128" s="46"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="9"/>
-      <c r="I128" s="10"/>
-      <c r="J128" s="32"/>
+      <c r="F128" s="36"/>
+      <c r="G128" s="31"/>
+      <c r="H128" s="14"/>
+      <c r="I128" s="14"/>
+      <c r="J128" s="44"/>
     </row>
     <row r="129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="25">
+      <c r="A129" s="20">
         <v>45875</v>
       </c>
-      <c r="B129" s="21">
+      <c r="B129" s="16">
         <v>1</v>
       </c>
       <c r="C129" s="7">
@@ -3883,17 +4055,19 @@
       <c r="E129" s="8">
         <v>0</v>
       </c>
-      <c r="F129" s="45"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="9"/>
-      <c r="I129" s="10"/>
-      <c r="J129" s="31"/>
+      <c r="F129" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" s="31"/>
+      <c r="H129" s="14"/>
+      <c r="I129" s="14"/>
+      <c r="J129" s="43"/>
     </row>
     <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="25">
+      <c r="A130" s="20">
         <v>45876</v>
       </c>
-      <c r="B130" s="21">
+      <c r="B130" s="16">
         <v>1</v>
       </c>
       <c r="C130" s="7">
@@ -3905,17 +4079,21 @@
       <c r="E130" s="8">
         <v>0</v>
       </c>
-      <c r="F130" s="45"/>
-      <c r="G130" s="9"/>
-      <c r="H130" s="9"/>
-      <c r="I130" s="10"/>
-      <c r="J130" s="31"/>
+      <c r="F130" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" s="14"/>
+      <c r="I130" s="14"/>
+      <c r="J130" s="43"/>
     </row>
     <row r="131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="25">
+      <c r="A131" s="20">
         <v>45877</v>
       </c>
-      <c r="B131" s="21">
+      <c r="B131" s="16">
         <v>1</v>
       </c>
       <c r="C131" s="7">
@@ -3927,17 +4105,21 @@
       <c r="E131" s="8">
         <v>0</v>
       </c>
-      <c r="F131" s="45"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="9"/>
-      <c r="I131" s="10"/>
-      <c r="J131" s="31"/>
+      <c r="F131" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H131" s="14"/>
+      <c r="I131" s="14"/>
+      <c r="J131" s="43"/>
     </row>
     <row r="132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="25">
+      <c r="A132" s="20">
         <v>45878</v>
       </c>
-      <c r="B132" s="22">
+      <c r="B132" s="17">
         <v>0</v>
       </c>
       <c r="C132" s="7">
@@ -3949,17 +4131,17 @@
       <c r="E132" s="8">
         <v>0</v>
       </c>
-      <c r="F132" s="46"/>
-      <c r="G132" s="9"/>
-      <c r="H132" s="9"/>
-      <c r="I132" s="10"/>
-      <c r="J132" s="32"/>
+      <c r="F132" s="36"/>
+      <c r="G132" s="31"/>
+      <c r="H132" s="14"/>
+      <c r="I132" s="14"/>
+      <c r="J132" s="44"/>
     </row>
     <row r="133" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="25">
+      <c r="A133" s="20">
         <v>45879</v>
       </c>
-      <c r="B133" s="22">
+      <c r="B133" s="17">
         <v>0</v>
       </c>
       <c r="C133" s="7">
@@ -3971,17 +4153,17 @@
       <c r="E133" s="8">
         <v>0</v>
       </c>
-      <c r="F133" s="46"/>
-      <c r="G133" s="9"/>
-      <c r="H133" s="9"/>
-      <c r="I133" s="10"/>
-      <c r="J133" s="32"/>
+      <c r="F133" s="36"/>
+      <c r="G133" s="31"/>
+      <c r="H133" s="14"/>
+      <c r="I133" s="14"/>
+      <c r="J133" s="44"/>
     </row>
     <row r="134" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="25">
+      <c r="A134" s="20">
         <v>45880</v>
       </c>
-      <c r="B134" s="22">
+      <c r="B134" s="17">
         <v>0</v>
       </c>
       <c r="C134" s="7">
@@ -3993,17 +4175,17 @@
       <c r="E134" s="8">
         <v>0</v>
       </c>
-      <c r="F134" s="46"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="10"/>
-      <c r="J134" s="32"/>
+      <c r="F134" s="36"/>
+      <c r="G134" s="31"/>
+      <c r="H134" s="14"/>
+      <c r="I134" s="14"/>
+      <c r="J134" s="44"/>
     </row>
     <row r="135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="25">
+      <c r="A135" s="20">
         <v>45881</v>
       </c>
-      <c r="B135" s="22">
+      <c r="B135" s="17">
         <v>0</v>
       </c>
       <c r="C135" s="7">
@@ -4015,17 +4197,17 @@
       <c r="E135" s="8">
         <v>0</v>
       </c>
-      <c r="F135" s="46"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
-      <c r="I135" s="10"/>
-      <c r="J135" s="32"/>
+      <c r="F135" s="36"/>
+      <c r="G135" s="31"/>
+      <c r="H135" s="14"/>
+      <c r="I135" s="14"/>
+      <c r="J135" s="44"/>
     </row>
     <row r="136" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="25">
+      <c r="A136" s="20">
         <v>45882</v>
       </c>
-      <c r="B136" s="22">
+      <c r="B136" s="17">
         <v>0</v>
       </c>
       <c r="C136" s="7">
@@ -4037,20 +4219,20 @@
       <c r="E136" s="8">
         <v>0</v>
       </c>
-      <c r="F136" s="46"/>
-      <c r="G136" s="9"/>
-      <c r="H136" s="9"/>
-      <c r="I136" s="10"/>
-      <c r="J136" s="32"/>
+      <c r="F136" s="36"/>
+      <c r="G136" s="31"/>
+      <c r="H136" s="14"/>
+      <c r="I136" s="14"/>
+      <c r="J136" s="44"/>
     </row>
     <row r="137" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="25">
+      <c r="A137" s="20">
         <v>45883</v>
       </c>
-      <c r="B137" s="22">
-        <v>0</v>
-      </c>
-      <c r="C137" s="11">
+      <c r="B137" s="17">
+        <v>0</v>
+      </c>
+      <c r="C137" s="9">
         <v>1</v>
       </c>
       <c r="D137" s="7">
@@ -4059,20 +4241,22 @@
       <c r="E137" s="8">
         <v>0</v>
       </c>
-      <c r="F137" s="45"/>
-      <c r="G137" s="9"/>
-      <c r="H137" s="9"/>
-      <c r="I137" s="10"/>
-      <c r="J137" s="31"/>
+      <c r="F137" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137" s="31"/>
+      <c r="H137" s="14"/>
+      <c r="I137" s="14"/>
+      <c r="J137" s="43"/>
     </row>
     <row r="138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="25">
+      <c r="A138" s="20">
         <v>45884</v>
       </c>
-      <c r="B138" s="22">
-        <v>0</v>
-      </c>
-      <c r="C138" s="11">
+      <c r="B138" s="17">
+        <v>0</v>
+      </c>
+      <c r="C138" s="9">
         <v>1</v>
       </c>
       <c r="D138" s="7">
@@ -4081,20 +4265,22 @@
       <c r="E138" s="8">
         <v>0</v>
       </c>
-      <c r="F138" s="45"/>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
-      <c r="I138" s="10"/>
-      <c r="J138" s="31"/>
+      <c r="F138" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G138" s="31"/>
+      <c r="H138" s="14"/>
+      <c r="I138" s="14"/>
+      <c r="J138" s="43"/>
     </row>
     <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="25">
+      <c r="A139" s="20">
         <v>45885</v>
       </c>
-      <c r="B139" s="22">
-        <v>0</v>
-      </c>
-      <c r="C139" s="11">
+      <c r="B139" s="17">
+        <v>0</v>
+      </c>
+      <c r="C139" s="9">
         <v>1</v>
       </c>
       <c r="D139" s="7">
@@ -4103,17 +4289,19 @@
       <c r="E139" s="8">
         <v>0</v>
       </c>
-      <c r="F139" s="45"/>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
-      <c r="I139" s="10"/>
-      <c r="J139" s="31"/>
+      <c r="F139" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G139" s="31"/>
+      <c r="H139" s="14"/>
+      <c r="I139" s="14"/>
+      <c r="J139" s="43"/>
     </row>
     <row r="140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="25">
+      <c r="A140" s="20">
         <v>45886</v>
       </c>
-      <c r="B140" s="22">
+      <c r="B140" s="17">
         <v>0</v>
       </c>
       <c r="C140" s="7">
@@ -4125,17 +4313,17 @@
       <c r="E140" s="8">
         <v>0</v>
       </c>
-      <c r="F140" s="46"/>
-      <c r="G140" s="9"/>
-      <c r="H140" s="9"/>
-      <c r="I140" s="10"/>
-      <c r="J140" s="32"/>
+      <c r="F140" s="36"/>
+      <c r="G140" s="31"/>
+      <c r="H140" s="14"/>
+      <c r="I140" s="14"/>
+      <c r="J140" s="44"/>
     </row>
     <row r="141" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="25">
+      <c r="A141" s="20">
         <v>45887</v>
       </c>
-      <c r="B141" s="22">
+      <c r="B141" s="17">
         <v>0</v>
       </c>
       <c r="C141" s="7">
@@ -4147,17 +4335,17 @@
       <c r="E141" s="8">
         <v>0</v>
       </c>
-      <c r="F141" s="46"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
-      <c r="I141" s="10"/>
-      <c r="J141" s="32"/>
+      <c r="F141" s="36"/>
+      <c r="G141" s="31"/>
+      <c r="H141" s="14"/>
+      <c r="I141" s="14"/>
+      <c r="J141" s="44"/>
     </row>
     <row r="142" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="25">
+      <c r="A142" s="20">
         <v>45888</v>
       </c>
-      <c r="B142" s="22">
+      <c r="B142" s="17">
         <v>0</v>
       </c>
       <c r="C142" s="7">
@@ -4169,17 +4357,17 @@
       <c r="E142" s="8">
         <v>0</v>
       </c>
-      <c r="F142" s="46"/>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="10"/>
-      <c r="J142" s="32"/>
+      <c r="F142" s="36"/>
+      <c r="G142" s="31"/>
+      <c r="H142" s="14"/>
+      <c r="I142" s="14"/>
+      <c r="J142" s="44"/>
     </row>
     <row r="143" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="25">
+      <c r="A143" s="20">
         <v>45889</v>
       </c>
-      <c r="B143" s="22">
+      <c r="B143" s="17">
         <v>0</v>
       </c>
       <c r="C143" s="7">
@@ -4191,17 +4379,17 @@
       <c r="E143" s="8">
         <v>0</v>
       </c>
-      <c r="F143" s="46"/>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
-      <c r="I143" s="10"/>
-      <c r="J143" s="32"/>
+      <c r="F143" s="36"/>
+      <c r="G143" s="31"/>
+      <c r="H143" s="14"/>
+      <c r="I143" s="14"/>
+      <c r="J143" s="44"/>
     </row>
     <row r="144" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="25">
+      <c r="A144" s="20">
         <v>45890</v>
       </c>
-      <c r="B144" s="22">
+      <c r="B144" s="17">
         <v>0</v>
       </c>
       <c r="C144" s="7">
@@ -4213,85 +4401,91 @@
       <c r="E144" s="8">
         <v>0</v>
       </c>
-      <c r="F144" s="46"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
-      <c r="I144" s="10"/>
-      <c r="J144" s="32"/>
+      <c r="F144" s="36"/>
+      <c r="G144" s="31"/>
+      <c r="H144" s="14"/>
+      <c r="I144" s="14"/>
+      <c r="J144" s="44"/>
     </row>
     <row r="145" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="25">
+      <c r="A145" s="20">
         <v>45891</v>
       </c>
-      <c r="B145" s="22">
+      <c r="B145" s="17">
         <v>0</v>
       </c>
       <c r="C145" s="7">
         <v>0</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="9">
         <v>1</v>
       </c>
       <c r="E145" s="8">
         <v>0</v>
       </c>
-      <c r="F145" s="48"/>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
-      <c r="I145" s="10"/>
-      <c r="J145" s="31"/>
+      <c r="F145" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G145" s="31"/>
+      <c r="H145" s="14"/>
+      <c r="I145" s="14"/>
+      <c r="J145" s="43"/>
     </row>
     <row r="146" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="25">
+      <c r="A146" s="20">
         <v>45892</v>
       </c>
-      <c r="B146" s="22">
+      <c r="B146" s="17">
         <v>0</v>
       </c>
       <c r="C146" s="7">
         <v>0</v>
       </c>
-      <c r="D146" s="11">
+      <c r="D146" s="9">
         <v>1</v>
       </c>
       <c r="E146" s="8">
         <v>0</v>
       </c>
-      <c r="F146" s="48"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
-      <c r="I146" s="10"/>
-      <c r="J146" s="31"/>
-    </row>
-    <row r="147" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="25">
+      <c r="F146" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146" s="31"/>
+      <c r="H146" s="14"/>
+      <c r="I146" s="14"/>
+      <c r="J146" s="43"/>
+    </row>
+    <row r="147" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="20">
         <v>45893</v>
       </c>
-      <c r="B147" s="22">
+      <c r="B147" s="17">
         <v>0</v>
       </c>
       <c r="C147" s="7">
         <v>0</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="9">
         <v>1</v>
       </c>
       <c r="E147" s="8">
         <v>0</v>
       </c>
-      <c r="F147" s="45"/>
-      <c r="G147" s="9"/>
-      <c r="H147" s="9"/>
-      <c r="I147" s="10"/>
-      <c r="J147" s="31"/>
-      <c r="L147" s="36"/>
-      <c r="M147" s="36"/>
-    </row>
-    <row r="148" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="25">
+      <c r="F147" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G147" s="31"/>
+      <c r="H147" s="14"/>
+      <c r="I147" s="14"/>
+      <c r="J147" s="43"/>
+      <c r="L147" s="23"/>
+      <c r="M147" s="23"/>
+    </row>
+    <row r="148" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="20">
         <v>45894</v>
       </c>
-      <c r="B148" s="22">
+      <c r="B148" s="17">
         <v>0</v>
       </c>
       <c r="C148" s="7">
@@ -4303,19 +4497,24 @@
       <c r="E148" s="8">
         <v>0</v>
       </c>
-      <c r="F148" s="46"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
-      <c r="I148" s="10"/>
-      <c r="J148" s="32"/>
-      <c r="L148" s="36"/>
-      <c r="M148" s="36"/>
+      <c r="F148" s="36"/>
+      <c r="G148" s="31"/>
+      <c r="H148" s="14"/>
+      <c r="I148" s="14"/>
+      <c r="J148" s="44"/>
+      <c r="L148" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="M148" s="28">
+        <f>COUNTIF(F2:F185,"Toloza")</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="149" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="25">
+      <c r="A149" s="20">
         <v>45895</v>
       </c>
-      <c r="B149" s="22">
+      <c r="B149" s="17">
         <v>0</v>
       </c>
       <c r="C149" s="7">
@@ -4327,813 +4526,839 @@
       <c r="E149" s="8">
         <v>0</v>
       </c>
-      <c r="F149" s="46"/>
-      <c r="G149" s="9"/>
-      <c r="H149" s="9"/>
-      <c r="I149" s="10"/>
-      <c r="J149" s="32"/>
-      <c r="L149" s="37" t="s">
+      <c r="F149" s="36"/>
+      <c r="G149" s="31"/>
+      <c r="H149" s="14"/>
+      <c r="I149" s="14"/>
+      <c r="J149" s="44"/>
+      <c r="L149" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="M149" s="29">
+        <f>COUNTIF(F2:F185,"Chacón")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="20">
+        <v>45896</v>
+      </c>
+      <c r="B150" s="17">
+        <v>0</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0</v>
+      </c>
+      <c r="D150" s="7">
+        <v>0</v>
+      </c>
+      <c r="E150" s="8">
+        <v>0</v>
+      </c>
+      <c r="F150" s="36"/>
+      <c r="G150" s="31"/>
+      <c r="H150" s="14"/>
+      <c r="I150" s="14"/>
+      <c r="J150" s="44"/>
+      <c r="L150" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M150" s="29">
+        <f>COUNTIF(F2:F185,"Rabus")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="20">
+        <v>45897</v>
+      </c>
+      <c r="B151" s="17">
+        <v>0</v>
+      </c>
+      <c r="C151" s="7">
+        <v>0</v>
+      </c>
+      <c r="D151" s="7">
+        <v>0</v>
+      </c>
+      <c r="E151" s="8">
+        <v>0</v>
+      </c>
+      <c r="F151" s="36"/>
+      <c r="G151" s="31"/>
+      <c r="H151" s="14"/>
+      <c r="I151" s="14"/>
+      <c r="J151" s="44"/>
+      <c r="L151" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M151" s="30">
+        <f>COUNTIF(F2:F183,"Schreiber ")</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="20">
+        <v>45898</v>
+      </c>
+      <c r="B152" s="17">
+        <v>0</v>
+      </c>
+      <c r="C152" s="7">
+        <v>0</v>
+      </c>
+      <c r="D152" s="7">
+        <v>0</v>
+      </c>
+      <c r="E152" s="8">
+        <v>0</v>
+      </c>
+      <c r="F152" s="36"/>
+      <c r="G152" s="31"/>
+      <c r="H152" s="14"/>
+      <c r="I152" s="14"/>
+      <c r="J152" s="44"/>
+      <c r="M152" s="11">
+        <f>SUM(M147:M151)</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="20">
+        <v>45899</v>
+      </c>
+      <c r="B153" s="17">
+        <v>0</v>
+      </c>
+      <c r="C153" s="7">
+        <v>0</v>
+      </c>
+      <c r="D153" s="7">
+        <v>0</v>
+      </c>
+      <c r="E153" s="10">
+        <v>1</v>
+      </c>
+      <c r="F153" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G153" s="31"/>
+      <c r="H153" s="14"/>
+      <c r="I153" s="14"/>
+      <c r="J153" s="43"/>
+    </row>
+    <row r="154" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="20">
+        <v>45900</v>
+      </c>
+      <c r="B154" s="17">
+        <v>0</v>
+      </c>
+      <c r="C154" s="7">
+        <v>0</v>
+      </c>
+      <c r="D154" s="7">
+        <v>0</v>
+      </c>
+      <c r="E154" s="10">
+        <v>1</v>
+      </c>
+      <c r="F154" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G154" s="31"/>
+      <c r="H154" s="14"/>
+      <c r="I154" s="14"/>
+      <c r="J154" s="44"/>
+    </row>
+    <row r="155" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="20">
+        <v>45901</v>
+      </c>
+      <c r="B155" s="17">
+        <v>0</v>
+      </c>
+      <c r="C155" s="7">
+        <v>0</v>
+      </c>
+      <c r="D155" s="7">
+        <v>0</v>
+      </c>
+      <c r="E155" s="10">
+        <v>1</v>
+      </c>
+      <c r="F155" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" s="31"/>
+      <c r="H155" s="14"/>
+      <c r="I155" s="14"/>
+      <c r="J155" s="44"/>
+    </row>
+    <row r="156" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="20">
+        <v>45902</v>
+      </c>
+      <c r="B156" s="17">
+        <v>0</v>
+      </c>
+      <c r="C156" s="7">
+        <v>0</v>
+      </c>
+      <c r="D156" s="7">
+        <v>0</v>
+      </c>
+      <c r="E156" s="8">
+        <v>0</v>
+      </c>
+      <c r="F156" s="36"/>
+      <c r="G156" s="31"/>
+      <c r="H156" s="14"/>
+      <c r="I156" s="14"/>
+      <c r="J156" s="44"/>
+    </row>
+    <row r="157" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="20">
+        <v>45903</v>
+      </c>
+      <c r="B157" s="17">
+        <v>0</v>
+      </c>
+      <c r="C157" s="7">
+        <v>0</v>
+      </c>
+      <c r="D157" s="7">
+        <v>0</v>
+      </c>
+      <c r="E157" s="8">
+        <v>0</v>
+      </c>
+      <c r="F157" s="36"/>
+      <c r="G157" s="31"/>
+      <c r="H157" s="14"/>
+      <c r="I157" s="14"/>
+      <c r="J157" s="44"/>
+    </row>
+    <row r="158" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="20">
+        <v>45904</v>
+      </c>
+      <c r="B158" s="17">
+        <v>0</v>
+      </c>
+      <c r="C158" s="7">
+        <v>0</v>
+      </c>
+      <c r="D158" s="7">
+        <v>0</v>
+      </c>
+      <c r="E158" s="8">
+        <v>0</v>
+      </c>
+      <c r="F158" s="36"/>
+      <c r="G158" s="31"/>
+      <c r="H158" s="14"/>
+      <c r="I158" s="14"/>
+      <c r="J158" s="44"/>
+    </row>
+    <row r="159" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="20">
+        <v>45905</v>
+      </c>
+      <c r="B159" s="17">
+        <v>0</v>
+      </c>
+      <c r="C159" s="7">
+        <v>0</v>
+      </c>
+      <c r="D159" s="7">
+        <v>0</v>
+      </c>
+      <c r="E159" s="8">
+        <v>0</v>
+      </c>
+      <c r="F159" s="36"/>
+      <c r="G159" s="31"/>
+      <c r="H159" s="14"/>
+      <c r="I159" s="14"/>
+      <c r="J159" s="44"/>
+    </row>
+    <row r="160" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="20">
+        <v>45906</v>
+      </c>
+      <c r="B160" s="17">
+        <v>0</v>
+      </c>
+      <c r="C160" s="7">
+        <v>0</v>
+      </c>
+      <c r="D160" s="7">
+        <v>0</v>
+      </c>
+      <c r="E160" s="8">
+        <v>0</v>
+      </c>
+      <c r="F160" s="36"/>
+      <c r="G160" s="31"/>
+      <c r="H160" s="14"/>
+      <c r="I160" s="14"/>
+      <c r="J160" s="44"/>
+    </row>
+    <row r="161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="20">
+        <v>45907</v>
+      </c>
+      <c r="B161" s="16">
+        <v>1</v>
+      </c>
+      <c r="C161" s="7">
+        <v>0</v>
+      </c>
+      <c r="D161" s="7">
+        <v>0</v>
+      </c>
+      <c r="E161" s="8">
+        <v>0</v>
+      </c>
+      <c r="F161" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G161" s="31"/>
+      <c r="H161" s="14"/>
+      <c r="I161" s="14"/>
+      <c r="J161" s="44"/>
+    </row>
+    <row r="162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="20">
+        <v>45908</v>
+      </c>
+      <c r="B162" s="16">
+        <v>1</v>
+      </c>
+      <c r="C162" s="7">
+        <v>0</v>
+      </c>
+      <c r="D162" s="7">
+        <v>0</v>
+      </c>
+      <c r="E162" s="8">
+        <v>0</v>
+      </c>
+      <c r="F162" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H162" s="14"/>
+      <c r="I162" s="14"/>
+      <c r="J162" s="44"/>
+    </row>
+    <row r="163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="20">
+        <v>45909</v>
+      </c>
+      <c r="B163" s="17">
+        <v>0</v>
+      </c>
+      <c r="C163" s="7">
+        <v>0</v>
+      </c>
+      <c r="D163" s="7">
+        <v>0</v>
+      </c>
+      <c r="E163" s="8">
+        <v>0</v>
+      </c>
+      <c r="F163" s="36"/>
+      <c r="G163" s="31"/>
+      <c r="H163" s="14"/>
+      <c r="I163" s="14"/>
+      <c r="J163" s="44"/>
+    </row>
+    <row r="164" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="20">
+        <v>45910</v>
+      </c>
+      <c r="B164" s="17">
+        <v>0</v>
+      </c>
+      <c r="C164" s="7">
+        <v>0</v>
+      </c>
+      <c r="D164" s="7">
+        <v>0</v>
+      </c>
+      <c r="E164" s="8">
+        <v>0</v>
+      </c>
+      <c r="F164" s="36"/>
+      <c r="G164" s="31"/>
+      <c r="H164" s="14"/>
+      <c r="I164" s="14"/>
+      <c r="J164" s="44"/>
+    </row>
+    <row r="165" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="20">
+        <v>45911</v>
+      </c>
+      <c r="B165" s="17">
+        <v>0</v>
+      </c>
+      <c r="C165" s="7">
+        <v>0</v>
+      </c>
+      <c r="D165" s="7">
+        <v>0</v>
+      </c>
+      <c r="E165" s="8">
+        <v>0</v>
+      </c>
+      <c r="F165" s="36"/>
+      <c r="G165" s="31"/>
+      <c r="H165" s="14"/>
+      <c r="I165" s="14"/>
+      <c r="J165" s="44"/>
+    </row>
+    <row r="166" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="20">
+        <v>45912</v>
+      </c>
+      <c r="B166" s="17">
+        <v>0</v>
+      </c>
+      <c r="C166" s="7">
+        <v>0</v>
+      </c>
+      <c r="D166" s="7">
+        <v>0</v>
+      </c>
+      <c r="E166" s="8">
+        <v>0</v>
+      </c>
+      <c r="F166" s="36"/>
+      <c r="G166" s="31"/>
+      <c r="H166" s="14"/>
+      <c r="I166" s="14"/>
+      <c r="J166" s="44"/>
+    </row>
+    <row r="167" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="20">
+        <v>45913</v>
+      </c>
+      <c r="B167" s="17">
+        <v>0</v>
+      </c>
+      <c r="C167" s="7">
+        <v>0</v>
+      </c>
+      <c r="D167" s="7">
+        <v>0</v>
+      </c>
+      <c r="E167" s="8">
+        <v>0</v>
+      </c>
+      <c r="F167" s="36"/>
+      <c r="G167" s="31"/>
+      <c r="H167" s="14"/>
+      <c r="I167" s="14"/>
+      <c r="J167" s="44"/>
+    </row>
+    <row r="168" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="20">
+        <v>45914</v>
+      </c>
+      <c r="B168" s="17">
+        <v>0</v>
+      </c>
+      <c r="C168" s="7">
+        <v>0</v>
+      </c>
+      <c r="D168" s="7">
+        <v>0</v>
+      </c>
+      <c r="E168" s="8">
+        <v>0</v>
+      </c>
+      <c r="F168" s="36"/>
+      <c r="G168" s="31"/>
+      <c r="H168" s="14"/>
+      <c r="I168" s="14"/>
+      <c r="J168" s="44"/>
+    </row>
+    <row r="169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="20">
+        <v>45915</v>
+      </c>
+      <c r="B169" s="17">
+        <v>0</v>
+      </c>
+      <c r="C169" s="9">
+        <v>1</v>
+      </c>
+      <c r="D169" s="7">
+        <v>0</v>
+      </c>
+      <c r="E169" s="8">
+        <v>0</v>
+      </c>
+      <c r="F169" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G169" s="31"/>
+      <c r="H169" s="14"/>
+      <c r="I169" s="14"/>
+      <c r="J169" s="44"/>
+    </row>
+    <row r="170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="20">
+        <v>45916</v>
+      </c>
+      <c r="B170" s="17">
+        <v>0</v>
+      </c>
+      <c r="C170" s="9">
+        <v>1</v>
+      </c>
+      <c r="D170" s="7">
+        <v>0</v>
+      </c>
+      <c r="E170" s="8">
+        <v>0</v>
+      </c>
+      <c r="F170" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H170" s="14"/>
+      <c r="I170" s="14"/>
+      <c r="J170" s="44"/>
+    </row>
+    <row r="171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="20">
+        <v>45917</v>
+      </c>
+      <c r="B171" s="17">
+        <v>0</v>
+      </c>
+      <c r="C171" s="7">
+        <v>0</v>
+      </c>
+      <c r="D171" s="7">
+        <v>0</v>
+      </c>
+      <c r="E171" s="8">
+        <v>0</v>
+      </c>
+      <c r="F171" s="36"/>
+      <c r="G171" s="31"/>
+      <c r="H171" s="14"/>
+      <c r="I171" s="14"/>
+      <c r="J171" s="44"/>
+    </row>
+    <row r="172" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="20">
+        <v>45918</v>
+      </c>
+      <c r="B172" s="17">
+        <v>0</v>
+      </c>
+      <c r="C172" s="7">
+        <v>0</v>
+      </c>
+      <c r="D172" s="7">
+        <v>0</v>
+      </c>
+      <c r="E172" s="8">
+        <v>0</v>
+      </c>
+      <c r="F172" s="36"/>
+      <c r="G172" s="31"/>
+      <c r="H172" s="14"/>
+      <c r="I172" s="14"/>
+      <c r="J172" s="44"/>
+    </row>
+    <row r="173" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="20">
+        <v>45919</v>
+      </c>
+      <c r="B173" s="17">
+        <v>0</v>
+      </c>
+      <c r="C173" s="7">
+        <v>0</v>
+      </c>
+      <c r="D173" s="7">
+        <v>0</v>
+      </c>
+      <c r="E173" s="8">
+        <v>0</v>
+      </c>
+      <c r="F173" s="36"/>
+      <c r="G173" s="31"/>
+      <c r="H173" s="14"/>
+      <c r="I173" s="14"/>
+      <c r="J173" s="44"/>
+    </row>
+    <row r="174" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="20">
+        <v>45920</v>
+      </c>
+      <c r="B174" s="17">
+        <v>0</v>
+      </c>
+      <c r="C174" s="7">
+        <v>0</v>
+      </c>
+      <c r="D174" s="7">
+        <v>0</v>
+      </c>
+      <c r="E174" s="8">
+        <v>0</v>
+      </c>
+      <c r="F174" s="36"/>
+      <c r="G174" s="31"/>
+      <c r="H174" s="14"/>
+      <c r="I174" s="14"/>
+      <c r="J174" s="44"/>
+    </row>
+    <row r="175" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="20">
+        <v>45921</v>
+      </c>
+      <c r="B175" s="17">
+        <v>0</v>
+      </c>
+      <c r="C175" s="7">
+        <v>0</v>
+      </c>
+      <c r="D175" s="7">
+        <v>0</v>
+      </c>
+      <c r="E175" s="8">
+        <v>0</v>
+      </c>
+      <c r="F175" s="36"/>
+      <c r="G175" s="31"/>
+      <c r="H175" s="14"/>
+      <c r="I175" s="14"/>
+      <c r="J175" s="44"/>
+    </row>
+    <row r="176" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="20">
+        <v>45922</v>
+      </c>
+      <c r="B176" s="17">
+        <v>0</v>
+      </c>
+      <c r="C176" s="7">
+        <v>0</v>
+      </c>
+      <c r="D176" s="7">
+        <v>0</v>
+      </c>
+      <c r="E176" s="8">
+        <v>0</v>
+      </c>
+      <c r="F176" s="36"/>
+      <c r="G176" s="31"/>
+      <c r="H176" s="14"/>
+      <c r="I176" s="14"/>
+      <c r="J176" s="44"/>
+    </row>
+    <row r="177" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="20">
+        <v>45923</v>
+      </c>
+      <c r="B177" s="17">
+        <v>0</v>
+      </c>
+      <c r="C177" s="7">
+        <v>0</v>
+      </c>
+      <c r="D177" s="9">
+        <v>1</v>
+      </c>
+      <c r="E177" s="8">
+        <v>0</v>
+      </c>
+      <c r="F177" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G177" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H177" s="14"/>
+      <c r="I177" s="14"/>
+      <c r="J177" s="44"/>
+    </row>
+    <row r="178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="20">
+        <v>45924</v>
+      </c>
+      <c r="B178" s="17">
+        <v>0</v>
+      </c>
+      <c r="C178" s="7">
+        <v>0</v>
+      </c>
+      <c r="D178" s="9">
+        <v>1</v>
+      </c>
+      <c r="E178" s="8">
+        <v>0</v>
+      </c>
+      <c r="F178" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G178" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H178" s="14"/>
+      <c r="I178" s="14"/>
+      <c r="J178" s="44"/>
+    </row>
+    <row r="179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="20">
+        <v>45925</v>
+      </c>
+      <c r="B179" s="17">
+        <v>0</v>
+      </c>
+      <c r="C179" s="7">
+        <v>0</v>
+      </c>
+      <c r="D179" s="7">
+        <v>0</v>
+      </c>
+      <c r="E179" s="8">
+        <v>0</v>
+      </c>
+      <c r="F179" s="36"/>
+      <c r="G179" s="31"/>
+      <c r="H179" s="14"/>
+      <c r="I179" s="14"/>
+      <c r="J179" s="44"/>
+    </row>
+    <row r="180" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="20">
+        <v>45926</v>
+      </c>
+      <c r="B180" s="17">
+        <v>0</v>
+      </c>
+      <c r="C180" s="7">
+        <v>0</v>
+      </c>
+      <c r="D180" s="7">
+        <v>0</v>
+      </c>
+      <c r="E180" s="8">
+        <v>0</v>
+      </c>
+      <c r="F180" s="36"/>
+      <c r="G180" s="31"/>
+      <c r="H180" s="14"/>
+      <c r="I180" s="14"/>
+      <c r="J180" s="44"/>
+    </row>
+    <row r="181" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="20">
+        <v>45927</v>
+      </c>
+      <c r="B181" s="17">
+        <v>0</v>
+      </c>
+      <c r="C181" s="7">
+        <v>0</v>
+      </c>
+      <c r="D181" s="7">
+        <v>0</v>
+      </c>
+      <c r="E181" s="8">
+        <v>0</v>
+      </c>
+      <c r="F181" s="36"/>
+      <c r="G181" s="31"/>
+      <c r="H181" s="14"/>
+      <c r="I181" s="14"/>
+      <c r="J181" s="44"/>
+    </row>
+    <row r="182" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="20">
+        <v>45928</v>
+      </c>
+      <c r="B182" s="17">
+        <v>0</v>
+      </c>
+      <c r="C182" s="7">
+        <v>0</v>
+      </c>
+      <c r="D182" s="7">
+        <v>0</v>
+      </c>
+      <c r="E182" s="8">
+        <v>0</v>
+      </c>
+      <c r="F182" s="36"/>
+      <c r="G182" s="31"/>
+      <c r="H182" s="14"/>
+      <c r="I182" s="14"/>
+      <c r="J182" s="44"/>
+    </row>
+    <row r="183" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="21">
+        <v>45929</v>
+      </c>
+      <c r="B183" s="17">
+        <v>0</v>
+      </c>
+      <c r="C183" s="7">
+        <v>0</v>
+      </c>
+      <c r="D183" s="7">
+        <v>0</v>
+      </c>
+      <c r="E183" s="8">
+        <v>0</v>
+      </c>
+      <c r="F183" s="39"/>
+      <c r="G183" s="45"/>
+      <c r="H183" s="46"/>
+      <c r="I183" s="46"/>
+      <c r="J183" s="47"/>
+    </row>
+    <row r="184" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="M149" s="38">
-        <f>COUNTIF(F2:F185," Pignata")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="25">
-        <v>45896</v>
-      </c>
-      <c r="B150" s="22">
-        <v>0</v>
-      </c>
-      <c r="C150" s="7">
-        <v>0</v>
-      </c>
-      <c r="D150" s="7">
-        <v>0</v>
-      </c>
-      <c r="E150" s="8">
-        <v>0</v>
-      </c>
-      <c r="F150" s="46"/>
-      <c r="G150" s="9"/>
-      <c r="H150" s="9"/>
-      <c r="I150" s="10"/>
-      <c r="J150" s="32"/>
-      <c r="L150" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="M150" s="40">
-        <f>COUNTIF(F2:F185,"Cáceres")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="25">
-        <v>45897</v>
-      </c>
-      <c r="B151" s="22">
-        <v>0</v>
-      </c>
-      <c r="C151" s="7">
-        <v>0</v>
-      </c>
-      <c r="D151" s="7">
-        <v>0</v>
-      </c>
-      <c r="E151" s="8">
-        <v>0</v>
-      </c>
-      <c r="F151" s="46"/>
-      <c r="G151" s="9"/>
-      <c r="H151" s="9"/>
-      <c r="I151" s="10"/>
-      <c r="J151" s="32"/>
-      <c r="L151" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="M151" s="42">
-        <f>COUNTIF(F2:F183,"Schreiber ")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="25">
-        <v>45898</v>
-      </c>
-      <c r="B152" s="22">
-        <v>0</v>
-      </c>
-      <c r="C152" s="7">
-        <v>0</v>
-      </c>
-      <c r="D152" s="7">
-        <v>0</v>
-      </c>
-      <c r="E152" s="8">
-        <v>0</v>
-      </c>
-      <c r="F152" s="46"/>
-      <c r="G152" s="9"/>
-      <c r="H152" s="9"/>
-      <c r="I152" s="10"/>
-      <c r="J152" s="32"/>
-      <c r="M152" s="13">
-        <f>SUM(M147:M151)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="25">
-        <v>45899</v>
-      </c>
-      <c r="B153" s="22">
-        <v>0</v>
-      </c>
-      <c r="C153" s="7">
-        <v>0</v>
-      </c>
-      <c r="D153" s="7">
-        <v>0</v>
-      </c>
-      <c r="E153" s="12">
-        <v>1</v>
-      </c>
-      <c r="F153" s="45"/>
-      <c r="G153" s="9"/>
-      <c r="H153" s="9"/>
-      <c r="I153" s="10"/>
-      <c r="J153" s="31"/>
-    </row>
-    <row r="154" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="25">
-        <v>45900</v>
-      </c>
-      <c r="B154" s="22">
-        <v>0</v>
-      </c>
-      <c r="C154" s="7">
-        <v>0</v>
-      </c>
-      <c r="D154" s="7">
-        <v>0</v>
-      </c>
-      <c r="E154" s="12">
-        <v>1</v>
-      </c>
-      <c r="F154" s="45"/>
-      <c r="G154" s="9"/>
-      <c r="H154" s="9"/>
-      <c r="I154" s="10"/>
-      <c r="J154" s="32"/>
-    </row>
-    <row r="155" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="25">
-        <v>45901</v>
-      </c>
-      <c r="B155" s="22">
-        <v>0</v>
-      </c>
-      <c r="C155" s="7">
-        <v>0</v>
-      </c>
-      <c r="D155" s="7">
-        <v>0</v>
-      </c>
-      <c r="E155" s="12">
-        <v>1</v>
-      </c>
-      <c r="F155" s="45"/>
-      <c r="G155" s="9"/>
-      <c r="H155" s="9"/>
-      <c r="I155" s="10"/>
-      <c r="J155" s="32"/>
-    </row>
-    <row r="156" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="25">
-        <v>45902</v>
-      </c>
-      <c r="B156" s="22">
-        <v>0</v>
-      </c>
-      <c r="C156" s="7">
-        <v>0</v>
-      </c>
-      <c r="D156" s="7">
-        <v>0</v>
-      </c>
-      <c r="E156" s="8">
-        <v>0</v>
-      </c>
-      <c r="F156" s="46"/>
-      <c r="G156" s="9"/>
-      <c r="H156" s="9"/>
-      <c r="I156" s="10"/>
-      <c r="J156" s="32"/>
-    </row>
-    <row r="157" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="25">
-        <v>45903</v>
-      </c>
-      <c r="B157" s="22">
-        <v>0</v>
-      </c>
-      <c r="C157" s="7">
-        <v>0</v>
-      </c>
-      <c r="D157" s="7">
-        <v>0</v>
-      </c>
-      <c r="E157" s="8">
-        <v>0</v>
-      </c>
-      <c r="F157" s="46"/>
-      <c r="G157" s="9"/>
-      <c r="H157" s="9"/>
-      <c r="I157" s="10"/>
-      <c r="J157" s="32"/>
-    </row>
-    <row r="158" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="25">
-        <v>45904</v>
-      </c>
-      <c r="B158" s="22">
-        <v>0</v>
-      </c>
-      <c r="C158" s="7">
-        <v>0</v>
-      </c>
-      <c r="D158" s="7">
-        <v>0</v>
-      </c>
-      <c r="E158" s="8">
-        <v>0</v>
-      </c>
-      <c r="F158" s="46"/>
-      <c r="G158" s="9"/>
-      <c r="H158" s="9"/>
-      <c r="I158" s="10"/>
-      <c r="J158" s="32"/>
-    </row>
-    <row r="159" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="25">
-        <v>45905</v>
-      </c>
-      <c r="B159" s="22">
-        <v>0</v>
-      </c>
-      <c r="C159" s="7">
-        <v>0</v>
-      </c>
-      <c r="D159" s="7">
-        <v>0</v>
-      </c>
-      <c r="E159" s="8">
-        <v>0</v>
-      </c>
-      <c r="F159" s="46"/>
-      <c r="G159" s="9"/>
-      <c r="H159" s="9"/>
-      <c r="I159" s="10"/>
-      <c r="J159" s="32"/>
-    </row>
-    <row r="160" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="25">
-        <v>45906</v>
-      </c>
-      <c r="B160" s="22">
-        <v>0</v>
-      </c>
-      <c r="C160" s="7">
-        <v>0</v>
-      </c>
-      <c r="D160" s="7">
-        <v>0</v>
-      </c>
-      <c r="E160" s="8">
-        <v>0</v>
-      </c>
-      <c r="F160" s="46"/>
-      <c r="G160" s="9"/>
-      <c r="H160" s="9"/>
-      <c r="I160" s="10"/>
-      <c r="J160" s="32"/>
-    </row>
-    <row r="161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="25">
-        <v>45907</v>
-      </c>
-      <c r="B161" s="21">
-        <v>1</v>
-      </c>
-      <c r="C161" s="7">
-        <v>0</v>
-      </c>
-      <c r="D161" s="7">
-        <v>0</v>
-      </c>
-      <c r="E161" s="8">
-        <v>0</v>
-      </c>
-      <c r="F161" s="48"/>
-      <c r="G161" s="9"/>
-      <c r="H161" s="9"/>
-      <c r="I161" s="10"/>
-      <c r="J161" s="32"/>
-    </row>
-    <row r="162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="25">
-        <v>45908</v>
-      </c>
-      <c r="B162" s="21">
-        <v>1</v>
-      </c>
-      <c r="C162" s="7">
-        <v>0</v>
-      </c>
-      <c r="D162" s="7">
-        <v>0</v>
-      </c>
-      <c r="E162" s="8">
-        <v>0</v>
-      </c>
-      <c r="F162" s="48"/>
-      <c r="G162" s="9"/>
-      <c r="H162" s="9"/>
-      <c r="I162" s="10"/>
-      <c r="J162" s="32"/>
-    </row>
-    <row r="163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="25">
-        <v>45909</v>
-      </c>
-      <c r="B163" s="22">
-        <v>0</v>
-      </c>
-      <c r="C163" s="7">
-        <v>0</v>
-      </c>
-      <c r="D163" s="7">
-        <v>0</v>
-      </c>
-      <c r="E163" s="8">
-        <v>0</v>
-      </c>
-      <c r="F163" s="46"/>
-      <c r="G163" s="9"/>
-      <c r="H163" s="9"/>
-      <c r="I163" s="10"/>
-      <c r="J163" s="32"/>
-    </row>
-    <row r="164" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="25">
-        <v>45910</v>
-      </c>
-      <c r="B164" s="22">
-        <v>0</v>
-      </c>
-      <c r="C164" s="7">
-        <v>0</v>
-      </c>
-      <c r="D164" s="7">
-        <v>0</v>
-      </c>
-      <c r="E164" s="8">
-        <v>0</v>
-      </c>
-      <c r="F164" s="46"/>
-      <c r="G164" s="9"/>
-      <c r="H164" s="9"/>
-      <c r="I164" s="10"/>
-      <c r="J164" s="32"/>
-    </row>
-    <row r="165" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="25">
-        <v>45911</v>
-      </c>
-      <c r="B165" s="22">
-        <v>0</v>
-      </c>
-      <c r="C165" s="7">
-        <v>0</v>
-      </c>
-      <c r="D165" s="7">
-        <v>0</v>
-      </c>
-      <c r="E165" s="8">
-        <v>0</v>
-      </c>
-      <c r="F165" s="46"/>
-      <c r="G165" s="9"/>
-      <c r="H165" s="9"/>
-      <c r="I165" s="10"/>
-      <c r="J165" s="32"/>
-    </row>
-    <row r="166" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="25">
-        <v>45912</v>
-      </c>
-      <c r="B166" s="22">
-        <v>0</v>
-      </c>
-      <c r="C166" s="7">
-        <v>0</v>
-      </c>
-      <c r="D166" s="7">
-        <v>0</v>
-      </c>
-      <c r="E166" s="8">
-        <v>0</v>
-      </c>
-      <c r="F166" s="46"/>
-      <c r="G166" s="9"/>
-      <c r="H166" s="9"/>
-      <c r="I166" s="10"/>
-      <c r="J166" s="32"/>
-    </row>
-    <row r="167" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="25">
-        <v>45913</v>
-      </c>
-      <c r="B167" s="22">
-        <v>0</v>
-      </c>
-      <c r="C167" s="7">
-        <v>0</v>
-      </c>
-      <c r="D167" s="7">
-        <v>0</v>
-      </c>
-      <c r="E167" s="8">
-        <v>0</v>
-      </c>
-      <c r="F167" s="46"/>
-      <c r="G167" s="9"/>
-      <c r="H167" s="9"/>
-      <c r="I167" s="10"/>
-      <c r="J167" s="32"/>
-    </row>
-    <row r="168" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="25">
-        <v>45914</v>
-      </c>
-      <c r="B168" s="22">
-        <v>0</v>
-      </c>
-      <c r="C168" s="7">
-        <v>0</v>
-      </c>
-      <c r="D168" s="7">
-        <v>0</v>
-      </c>
-      <c r="E168" s="8">
-        <v>0</v>
-      </c>
-      <c r="F168" s="46"/>
-      <c r="G168" s="9"/>
-      <c r="H168" s="9"/>
-      <c r="I168" s="10"/>
-      <c r="J168" s="32"/>
-    </row>
-    <row r="169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="25">
-        <v>45915</v>
-      </c>
-      <c r="B169" s="22">
-        <v>0</v>
-      </c>
-      <c r="C169" s="11">
-        <v>1</v>
-      </c>
-      <c r="D169" s="7">
-        <v>0</v>
-      </c>
-      <c r="E169" s="8">
-        <v>0</v>
-      </c>
-      <c r="F169" s="45"/>
-      <c r="G169" s="9"/>
-      <c r="H169" s="9"/>
-      <c r="I169" s="10"/>
-      <c r="J169" s="32"/>
-    </row>
-    <row r="170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="25">
-        <v>45916</v>
-      </c>
-      <c r="B170" s="22">
-        <v>0</v>
-      </c>
-      <c r="C170" s="11">
-        <v>1</v>
-      </c>
-      <c r="D170" s="7">
-        <v>0</v>
-      </c>
-      <c r="E170" s="8">
-        <v>0</v>
-      </c>
-      <c r="F170" s="45"/>
-      <c r="G170" s="9"/>
-      <c r="H170" s="9"/>
-      <c r="I170" s="10"/>
-      <c r="J170" s="32"/>
-    </row>
-    <row r="171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="25">
-        <v>45917</v>
-      </c>
-      <c r="B171" s="22">
-        <v>0</v>
-      </c>
-      <c r="C171" s="7">
-        <v>0</v>
-      </c>
-      <c r="D171" s="7">
-        <v>0</v>
-      </c>
-      <c r="E171" s="8">
-        <v>0</v>
-      </c>
-      <c r="F171" s="46"/>
-      <c r="G171" s="9"/>
-      <c r="H171" s="9"/>
-      <c r="I171" s="10"/>
-      <c r="J171" s="32"/>
-    </row>
-    <row r="172" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="25">
-        <v>45918</v>
-      </c>
-      <c r="B172" s="22">
-        <v>0</v>
-      </c>
-      <c r="C172" s="7">
-        <v>0</v>
-      </c>
-      <c r="D172" s="7">
-        <v>0</v>
-      </c>
-      <c r="E172" s="8">
-        <v>0</v>
-      </c>
-      <c r="F172" s="46"/>
-      <c r="G172" s="9"/>
-      <c r="H172" s="9"/>
-      <c r="I172" s="10"/>
-      <c r="J172" s="32"/>
-    </row>
-    <row r="173" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="25">
-        <v>45919</v>
-      </c>
-      <c r="B173" s="22">
-        <v>0</v>
-      </c>
-      <c r="C173" s="7">
-        <v>0</v>
-      </c>
-      <c r="D173" s="7">
-        <v>0</v>
-      </c>
-      <c r="E173" s="8">
-        <v>0</v>
-      </c>
-      <c r="F173" s="46"/>
-      <c r="G173" s="9"/>
-      <c r="H173" s="9"/>
-      <c r="I173" s="10"/>
-      <c r="J173" s="32"/>
-    </row>
-    <row r="174" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="25">
-        <v>45920</v>
-      </c>
-      <c r="B174" s="22">
-        <v>0</v>
-      </c>
-      <c r="C174" s="7">
-        <v>0</v>
-      </c>
-      <c r="D174" s="7">
-        <v>0</v>
-      </c>
-      <c r="E174" s="8">
-        <v>0</v>
-      </c>
-      <c r="F174" s="46"/>
-      <c r="G174" s="9"/>
-      <c r="H174" s="9"/>
-      <c r="I174" s="10"/>
-      <c r="J174" s="32"/>
-    </row>
-    <row r="175" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="25">
-        <v>45921</v>
-      </c>
-      <c r="B175" s="22">
-        <v>0</v>
-      </c>
-      <c r="C175" s="7">
-        <v>0</v>
-      </c>
-      <c r="D175" s="7">
-        <v>0</v>
-      </c>
-      <c r="E175" s="8">
-        <v>0</v>
-      </c>
-      <c r="F175" s="46"/>
-      <c r="G175" s="9"/>
-      <c r="H175" s="9"/>
-      <c r="I175" s="10"/>
-      <c r="J175" s="32"/>
-    </row>
-    <row r="176" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="25">
-        <v>45922</v>
-      </c>
-      <c r="B176" s="22">
-        <v>0</v>
-      </c>
-      <c r="C176" s="7">
-        <v>0</v>
-      </c>
-      <c r="D176" s="7">
-        <v>0</v>
-      </c>
-      <c r="E176" s="8">
-        <v>0</v>
-      </c>
-      <c r="F176" s="46"/>
-      <c r="G176" s="9"/>
-      <c r="H176" s="9"/>
-      <c r="I176" s="10"/>
-      <c r="J176" s="32"/>
-    </row>
-    <row r="177" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="25">
-        <v>45923</v>
-      </c>
-      <c r="B177" s="22">
-        <v>0</v>
-      </c>
-      <c r="C177" s="7">
-        <v>0</v>
-      </c>
-      <c r="D177" s="11">
-        <v>1</v>
-      </c>
-      <c r="E177" s="8">
-        <v>0</v>
-      </c>
-      <c r="F177" s="45"/>
-      <c r="G177" s="9"/>
-      <c r="H177" s="9"/>
-      <c r="I177" s="10"/>
-      <c r="J177" s="32"/>
-    </row>
-    <row r="178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="25">
-        <v>45924</v>
-      </c>
-      <c r="B178" s="22">
-        <v>0</v>
-      </c>
-      <c r="C178" s="7">
-        <v>0</v>
-      </c>
-      <c r="D178" s="11">
-        <v>1</v>
-      </c>
-      <c r="E178" s="8">
-        <v>0</v>
-      </c>
-      <c r="F178" s="48"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
-      <c r="I178" s="10"/>
-      <c r="J178" s="32"/>
-    </row>
-    <row r="179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="25">
-        <v>45925</v>
-      </c>
-      <c r="B179" s="22">
-        <v>0</v>
-      </c>
-      <c r="C179" s="7">
-        <v>0</v>
-      </c>
-      <c r="D179" s="7">
-        <v>0</v>
-      </c>
-      <c r="E179" s="8">
-        <v>0</v>
-      </c>
-      <c r="F179" s="46"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="9"/>
-      <c r="I179" s="10"/>
-      <c r="J179" s="32"/>
-    </row>
-    <row r="180" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="25">
-        <v>45926</v>
-      </c>
-      <c r="B180" s="22">
-        <v>0</v>
-      </c>
-      <c r="C180" s="7">
-        <v>0</v>
-      </c>
-      <c r="D180" s="7">
-        <v>0</v>
-      </c>
-      <c r="E180" s="8">
-        <v>0</v>
-      </c>
-      <c r="F180" s="46"/>
-      <c r="G180" s="9"/>
-      <c r="H180" s="9"/>
-      <c r="I180" s="10"/>
-      <c r="J180" s="32"/>
-    </row>
-    <row r="181" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="25">
-        <v>45927</v>
-      </c>
-      <c r="B181" s="22">
-        <v>0</v>
-      </c>
-      <c r="C181" s="7">
-        <v>0</v>
-      </c>
-      <c r="D181" s="7">
-        <v>0</v>
-      </c>
-      <c r="E181" s="8">
-        <v>0</v>
-      </c>
-      <c r="F181" s="46"/>
-      <c r="G181" s="9"/>
-      <c r="H181" s="9"/>
-      <c r="I181" s="10"/>
-      <c r="J181" s="32"/>
-    </row>
-    <row r="182" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="25">
-        <v>45928</v>
-      </c>
-      <c r="B182" s="22">
-        <v>0</v>
-      </c>
-      <c r="C182" s="7">
-        <v>0</v>
-      </c>
-      <c r="D182" s="7">
-        <v>0</v>
-      </c>
-      <c r="E182" s="8">
-        <v>0</v>
-      </c>
-      <c r="F182" s="46"/>
-      <c r="G182" s="9"/>
-      <c r="H182" s="9"/>
-      <c r="I182" s="10"/>
-      <c r="J182" s="32"/>
-    </row>
-    <row r="183" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="26">
-        <v>45929</v>
-      </c>
-      <c r="B183" s="22">
-        <v>0</v>
-      </c>
-      <c r="C183" s="7">
-        <v>0</v>
-      </c>
-      <c r="D183" s="7">
-        <v>0</v>
-      </c>
-      <c r="E183" s="8">
-        <v>0</v>
-      </c>
-      <c r="F183" s="49"/>
-      <c r="G183" s="33"/>
-      <c r="H183" s="33"/>
-      <c r="I183" s="34"/>
-      <c r="J183" s="35"/>
-    </row>
-    <row r="184" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B184" s="14">
+      <c r="B184" s="12">
         <f>SUM(B2:B183)</f>
         <v>17</v>
       </c>
-      <c r="C184" s="14">
+      <c r="C184" s="12">
         <f>SUM(C2:C183)</f>
-        <v>17</v>
-      </c>
-      <c r="D184" s="14">
+        <v>18</v>
+      </c>
+      <c r="D184" s="12">
         <f>SUM(D2:D183)</f>
         <v>17</v>
       </c>
-      <c r="E184" s="14">
+      <c r="E184" s="12">
         <f>SUM(E2:E183)</f>
         <v>15</v>
       </c>
-      <c r="F184" s="43">
+      <c r="F184" s="24">
         <f>SUM(B184:E184)</f>
-        <v>66</v>
-      </c>
-      <c r="G184" s="15"/>
-      <c r="H184" s="15"/>
-      <c r="I184" s="15"/>
-      <c r="J184" s="27">
+        <v>67</v>
+      </c>
+      <c r="G184" s="13"/>
+      <c r="H184" s="13"/>
+      <c r="I184" s="13"/>
+      <c r="J184" s="22">
         <f>COUNTIF(J1:J183,"True")</f>
         <v>0</v>
       </c>
